--- a/src/attributions/attributions_saliency_traj_62.xlsx
+++ b/src/attributions/attributions_saliency_traj_62.xlsx
@@ -999,571 +999,571 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.0004090412403456867</v>
+        <v>9.951255097728762e-12</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02699384652078152</v>
+        <v>3.778009502464208e-11</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007491347496397793</v>
+        <v>2.037783136676907e-11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007611353415995836</v>
+        <v>2.791326718376563e-11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.005055753514170647</v>
+        <v>5.145278994533875e-11</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01243515871465206</v>
+        <v>6.862160839560261e-11</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001642400166019797</v>
+        <v>4.023727184776504e-11</v>
       </c>
       <c r="H2" t="n">
-        <v>0.01777839846909046</v>
+        <v>1.002701610977597e-12</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02791700325906277</v>
+        <v>6.759068998940521e-12</v>
       </c>
       <c r="J2" t="n">
-        <v>0.005998985841870308</v>
+        <v>1.304428613735364e-11</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02040739357471466</v>
+        <v>7.234576826498085e-11</v>
       </c>
       <c r="L2" t="n">
-        <v>2.758530899882317e-05</v>
+        <v>8.149664970646953e-12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01761376857757568</v>
+        <v>2.847012209317157e-11</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002107754349708557</v>
+        <v>6.69048150214735e-11</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01177569758147001</v>
+        <v>9.839089959440273e-11</v>
       </c>
       <c r="P2" t="n">
-        <v>0.004193746950477362</v>
+        <v>2.051095578103901e-11</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01175238005816936</v>
+        <v>3.266876699714594e-11</v>
       </c>
       <c r="R2" t="n">
-        <v>0.02769133262336254</v>
+        <v>1.422598757544469e-11</v>
       </c>
       <c r="S2" t="n">
-        <v>0.002105000661686063</v>
+        <v>8.713660869241746e-12</v>
       </c>
       <c r="T2" t="n">
-        <v>0.001135578379034996</v>
+        <v>1.07289004069866e-11</v>
       </c>
       <c r="U2" t="n">
-        <v>0.004594718106091022</v>
+        <v>6.813105635217198e-12</v>
       </c>
       <c r="V2" t="n">
-        <v>0.001529138069599867</v>
+        <v>2.813431085324503e-11</v>
       </c>
       <c r="W2" t="n">
-        <v>0.002133653732016683</v>
+        <v>1.090860995284215e-11</v>
       </c>
       <c r="X2" t="n">
-        <v>0.009275980293750763</v>
+        <v>1.195175685850258e-12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0001204267900902778</v>
+        <v>1.464392149208571e-11</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.001299710595048964</v>
+        <v>1.907309726822959e-11</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0022443444468081</v>
+        <v>4.122149670215958e-12</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.006095580291002989</v>
+        <v>1.880866122572211e-12</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0009125154465436935</v>
+        <v>5.286713341406957e-12</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.01518395077437162</v>
+        <v>2.693014214405487e-11</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.002106142928823829</v>
+        <v>5.815533818398499e-11</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0001901104114949703</v>
+        <v>4.18853250694351e-11</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.004912058357149363</v>
+        <v>1.413194040955634e-11</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.004280923865735531</v>
+        <v>9.258390928912341e-12</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.002332820557057858</v>
+        <v>2.579807721614369e-11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.001419260166585445</v>
+        <v>1.812620019359112e-11</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.002768927253782749</v>
+        <v>1.1213944703381e-11</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.001046070596203208</v>
+        <v>1.698191240406821e-11</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.001700633787550032</v>
+        <v>2.27640801174489e-12</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.001561796292662621</v>
+        <v>7.313550806631319e-12</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.004417357034981251</v>
+        <v>1.463176801941302e-11</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.002603535074740648</v>
+        <v>2.024867946925912e-11</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.001920192851684988</v>
+        <v>2.459856277003958e-11</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.0008986648172140121</v>
+        <v>1.202549865242375e-11</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.002997978590428829</v>
+        <v>8.011357202630798e-12</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0009849033085629344</v>
+        <v>4.643867321935113e-12</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.02691733092069626</v>
+        <v>1.100773777684694e-10</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.005191692151129246</v>
+        <v>2.801010942285465e-12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0009536574361845851</v>
+        <v>2.140555961649415e-12</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.02215858921408653</v>
+        <v>1.138200471373363e-11</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.001186423236504197</v>
+        <v>1.843420902036819e-11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.005944941192865372</v>
+        <v>1.494839148297178e-11</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.00538515904918313</v>
+        <v>2.083369587957407e-11</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.005050963256508112</v>
+        <v>1.755015837517915e-12</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.004294943064451218</v>
+        <v>6.473387798022756e-12</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.001087642274796963</v>
+        <v>4.476528869812313e-11</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.003580590477213264</v>
+        <v>1.38779942399081e-11</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.001756644807755947</v>
+        <v>3.253004809966598e-11</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.003672139253467321</v>
+        <v>6.821185977168298e-11</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.01559454668313265</v>
+        <v>5.31323492147795e-11</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.001689962344244123</v>
+        <v>1.713181332907432e-11</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.005232334602624178</v>
+        <v>9.980767080863817e-12</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.02612435445189476</v>
+        <v>1.170769384217785e-11</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.003550184657797217</v>
+        <v>1.62628209510185e-11</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0001858859322965145</v>
+        <v>2.113734881570295e-11</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.001976637402549386</v>
+        <v>7.377263730456995e-12</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0009066285565495491</v>
+        <v>5.784319637852642e-12</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.02282570861279964</v>
+        <v>3.157183542379371e-11</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.00673892255872488</v>
+        <v>2.029965258387723e-11</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.006035078782588243</v>
+        <v>4.471122430627084e-11</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.002588376868516207</v>
+        <v>1.02016849828912e-11</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.008760870434343815</v>
+        <v>1.785225786643529e-11</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.001094601815566421</v>
+        <v>8.880557747503737e-12</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.0154092088341713</v>
+        <v>5.483107717862978e-11</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.006046425551176071</v>
+        <v>5.890289124510506e-12</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.001525337225757539</v>
+        <v>4.477133941360734e-12</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.006219428963959217</v>
+        <v>2.846881758111763e-11</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.003907156176865101</v>
+        <v>2.246122125099115e-12</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.0004759461735375226</v>
+        <v>1.298768037560905e-11</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.004236277192831039</v>
+        <v>2.611168226085425e-11</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.00362837640568614</v>
+        <v>8.153356462203831e-12</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.0003144932561554015</v>
+        <v>6.381133468846834e-12</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.004660195671021938</v>
+        <v>1.643562369535445e-11</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.002930277958512306</v>
+        <v>2.896317083736499e-12</v>
       </c>
       <c r="CG2" t="n">
-        <v>8.500840340275317e-05</v>
+        <v>1.272438925059571e-11</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.001301422365941107</v>
+        <v>1.392504948155571e-11</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.001174350269138813</v>
+        <v>1.447332618337294e-11</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.001905757701024413</v>
+        <v>1.672864624602255e-11</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.002928392961621284</v>
+        <v>2.952720967036582e-12</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.007036308757960796</v>
+        <v>1.772985838005559e-12</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.008509236387908459</v>
+        <v>2.996930481558024e-11</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.006160559598356485</v>
+        <v>5.43393524621294e-11</v>
       </c>
       <c r="CO2" t="n">
-        <v>0.0007892040885053575</v>
+        <v>9.425938328477823e-12</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.008005899377167225</v>
+        <v>5.344905074089468e-11</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.01064194925129414</v>
+        <v>5.735976971177337e-11</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.006935223937034607</v>
+        <v>6.616019364302783e-12</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.002608414739370346</v>
+        <v>5.230512637593998e-12</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.00974792055785656</v>
+        <v>2.1358055948828e-11</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.006284109782427549</v>
+        <v>1.240440736238746e-11</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.0001950685691554099</v>
+        <v>1.180548367396561e-11</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.005122276954352856</v>
+        <v>1.650527804708535e-11</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.002666151616722345</v>
+        <v>2.000288172945841e-12</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0003644166863523424</v>
+        <v>9.836032162369168e-12</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.0005617411225102842</v>
+        <v>1.017418961579697e-11</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.0004083107924088836</v>
+        <v>1.687728255761467e-11</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.001862784498371184</v>
+        <v>8.470156000195406e-12</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.002487949095666409</v>
+        <v>5.212633710088843e-12</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.005151105113327503</v>
+        <v>5.013989657493001e-12</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.003985542338341475</v>
+        <v>1.270875418790673e-11</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.003687832737341523</v>
+        <v>1.695881499466645e-12</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.004796176217496395</v>
+        <v>9.636047168526396e-12</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.006749233230948448</v>
+        <v>1.58705670133541e-11</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.001932529383338988</v>
+        <v>5.418982970684105e-12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.003249363973736763</v>
+        <v>8.628886667694236e-12</v>
       </c>
       <c r="DK2" t="n">
-        <v>0.003584099467843771</v>
+        <v>2.950776428756186e-11</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.01393192820250988</v>
+        <v>1.344281023302196e-11</v>
       </c>
       <c r="DM2" t="n">
-        <v>7.054791785776615e-05</v>
+        <v>9.913600322597471e-12</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.002267258008942008</v>
+        <v>8.617854693748761e-13</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.001699493732303381</v>
+        <v>9.806855848226714e-12</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.003020163625478745</v>
+        <v>1.063412205515313e-11</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.003412616904824972</v>
+        <v>2.958561173826979e-11</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0021134321577847</v>
+        <v>3.787800628707316e-11</v>
       </c>
       <c r="DS2" t="n">
-        <v>8.187582716345787e-05</v>
+        <v>2.568294708849006e-11</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.002108425600454211</v>
+        <v>3.44933595575192e-11</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.001420319080352783</v>
+        <v>2.645640477527689e-11</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.007925025187432766</v>
+        <v>8.622939168256849e-12</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.0007846814696677029</v>
+        <v>1.536087576581302e-11</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.01053351722657681</v>
+        <v>2.059520609609677e-11</v>
       </c>
       <c r="DY2" t="n">
-        <v>0.002475787419825792</v>
+        <v>2.258248622821757e-11</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.001192264258861542</v>
+        <v>1.14312326965349e-11</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.002174680121243</v>
+        <v>1.22016416068127e-11</v>
       </c>
       <c r="EB2" t="n">
-        <v>0.005595489870756865</v>
+        <v>7.653384870298652e-12</v>
       </c>
       <c r="EC2" t="n">
-        <v>0.002590979682281613</v>
+        <v>1.191832223190747e-12</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.004899545572698116</v>
+        <v>4.316327156805855e-11</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.003444273956120014</v>
+        <v>9.330276135033344e-12</v>
       </c>
       <c r="EF2" t="n">
-        <v>0.001027242979034781</v>
+        <v>1.860192902491953e-11</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.003933800384402275</v>
+        <v>5.690101168021044e-13</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.005038994830101728</v>
+        <v>3.148030447430727e-12</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.002908751834183931</v>
+        <v>1.332013926241826e-11</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.0008092740899883211</v>
+        <v>2.296400916645958e-12</v>
       </c>
       <c r="EK2" t="n">
-        <v>0.0009758482920005918</v>
+        <v>8.74927040539486e-12</v>
       </c>
       <c r="EL2" t="n">
-        <v>0.002644366817548871</v>
+        <v>1.054188160376501e-11</v>
       </c>
       <c r="EM2" t="n">
-        <v>0.002760943723842502</v>
+        <v>8.101212409239444e-12</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.007665093056857586</v>
+        <v>5.293182125248874e-12</v>
       </c>
       <c r="EO2" t="n">
-        <v>0.0022263762075454</v>
+        <v>6.588198736556805e-12</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.002944538602605462</v>
+        <v>8.122712572000701e-14</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.00388280488550663</v>
+        <v>4.498533056479515e-12</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.002492759609594941</v>
+        <v>5.792563043810484e-12</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.005134982522577047</v>
+        <v>1.401773575687715e-11</v>
       </c>
       <c r="ET2" t="n">
-        <v>0.003993449732661247</v>
+        <v>2.694271455244701e-12</v>
       </c>
       <c r="EU2" t="n">
-        <v>0.002648412249982357</v>
+        <v>8.629680303684495e-12</v>
       </c>
       <c r="EV2" t="n">
-        <v>0.001564147067256272</v>
+        <v>2.14264318093571e-11</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.003357816953212023</v>
+        <v>2.361176705545365e-11</v>
       </c>
       <c r="EX2" t="n">
-        <v>0.001508274348452687</v>
+        <v>9.450950438916195e-12</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.005712586920708418</v>
+        <v>2.00627466029335e-11</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0.002287240931764245</v>
+        <v>2.121204037072721e-12</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.001373268547467887</v>
+        <v>9.592788369205962e-12</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.0001052189763868228</v>
+        <v>1.215426197187508e-11</v>
       </c>
       <c r="FC2" t="n">
-        <v>0.001838861382566392</v>
+        <v>9.036459081013248e-12</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.0020653719548136</v>
+        <v>1.026879189319763e-11</v>
       </c>
       <c r="FE2" t="n">
-        <v>0.002430200111120939</v>
+        <v>6.343862067603734e-12</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.005665887147188187</v>
+        <v>1.388272634871013e-13</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.001630163169465959</v>
+        <v>1.492762163879391e-11</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.002111775800585747</v>
+        <v>1.242093147085788e-11</v>
       </c>
       <c r="FI2" t="n">
-        <v>0.001849506050348282</v>
+        <v>6.812313733950415e-12</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.002367843175306916</v>
+        <v>1.701297956679948e-11</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.006675688084214926</v>
+        <v>9.944148803009423e-12</v>
       </c>
       <c r="FL2" t="n">
-        <v>0.0002891053445637226</v>
+        <v>8.891579963629659e-14</v>
       </c>
       <c r="FM2" t="n">
-        <v>8.578953566029668e-05</v>
+        <v>2.939303748311639e-12</v>
       </c>
       <c r="FN2" t="n">
-        <v>0.001509478781372309</v>
+        <v>2.61731730039072e-11</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.0008615246042609215</v>
+        <v>8.5046874057082e-12</v>
       </c>
       <c r="FP2" t="n">
-        <v>0.003233654424548149</v>
+        <v>2.873634316613582e-11</v>
       </c>
       <c r="FQ2" t="n">
-        <v>0.0002388851717114449</v>
+        <v>4.323638322367707e-11</v>
       </c>
       <c r="FR2" t="n">
-        <v>0.004315497353672981</v>
+        <v>1.601856494670706e-11</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.001646636985242367</v>
+        <v>1.67079180352081e-11</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.006404714658856392</v>
+        <v>6.473309301785468e-12</v>
       </c>
       <c r="FU2" t="n">
-        <v>0.005717512685805559</v>
+        <v>1.072943556917894e-11</v>
       </c>
       <c r="FV2" t="n">
-        <v>0.008751906454563141</v>
+        <v>2.196925801001282e-11</v>
       </c>
       <c r="FW2" t="n">
-        <v>0.002962956903502345</v>
+        <v>2.613525021399887e-11</v>
       </c>
       <c r="FX2" t="n">
-        <v>0.002962597645819187</v>
+        <v>8.833302145294653e-12</v>
       </c>
       <c r="FY2" t="n">
-        <v>0.005004758015275002</v>
+        <v>3.282978489754784e-12</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.003118860069662333</v>
+        <v>2.255561622893643e-12</v>
       </c>
       <c r="GA2" t="n">
-        <v>0.004483654629439116</v>
+        <v>1.793992905618769e-12</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.00588827021420002</v>
+        <v>1.314902527138617e-11</v>
       </c>
       <c r="GC2" t="n">
-        <v>0.001305672689341009</v>
+        <v>1.079738078460513e-12</v>
       </c>
       <c r="GD2" t="n">
-        <v>0.00569768063724041</v>
+        <v>2.050230818451126e-11</v>
       </c>
       <c r="GE2" t="n">
-        <v>0.003399390028789639</v>
+        <v>2.036533441884814e-11</v>
       </c>
       <c r="GF2" t="n">
-        <v>0.00244759046472609</v>
+        <v>4.304019380479973e-12</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.001321692601777613</v>
+        <v>3.968215513128204e-12</v>
       </c>
     </row>
     <row r="3">
@@ -2706,571 +2706,571 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.001823190599679947</v>
+        <v>6.625397119819354e-09</v>
       </c>
       <c r="B5" t="n">
-        <v>0.016232680529356</v>
+        <v>1.479656064340418e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003957886248826981</v>
+        <v>2.269476828686834e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005648873746395111</v>
+        <v>2.611798555207656e-10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008064805530011654</v>
+        <v>3.462822473210281e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003733607474714518</v>
+        <v>1.006236760581203e-10</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01001240313053131</v>
+        <v>9.507931331143027e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0002570764627307653</v>
+        <v>9.387105315283861e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.009815272875130177</v>
+        <v>3.328918918299451e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004122588317841291</v>
+        <v>5.830627536340671e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01634147763252258</v>
+        <v>9.307187798235361e-10</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003216171637177467</v>
+        <v>2.998989501179494e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003688236232846975</v>
+        <v>5.531965996397048e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>0.009508064016699791</v>
+        <v>5.682001535944892e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0006267561111599207</v>
+        <v>1.801257698552661e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>0.00698092533275485</v>
+        <v>1.36286368856986e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0006245151744224131</v>
+        <v>7.474858065847911e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>0.008517278358340263</v>
+        <v>2.605279325607057e-10</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001995858270674944</v>
+        <v>1.794137283184227e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>0.005015947390347719</v>
+        <v>2.253659481254999e-10</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0004270285135135055</v>
+        <v>2.24536478299342e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.005367682315409184</v>
+        <v>3.445739693574978e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>0.01140386424958706</v>
+        <v>2.560084144676011e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>0.00440191850066185</v>
+        <v>2.316794756040963e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.00183233292773366</v>
+        <v>3.127555325832532e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.001067275181412697</v>
+        <v>6.553634301909028e-10</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004926908877678216</v>
+        <v>3.295838935102324e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.003911144565790892</v>
+        <v>1.022099915815033e-08</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.003371477127075195</v>
+        <v>8.812609308961328e-09</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.006837742403149605</v>
+        <v>2.21056239979589e-09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.002451263833791018</v>
+        <v>9.274898626898676e-10</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0005940943956375122</v>
+        <v>3.557272032495007e-09</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.002906476147472858</v>
+        <v>2.670993648479225e-09</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0003800490230787545</v>
+        <v>9.311603710315808e-10</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.004475443158298731</v>
+        <v>5.225799348806959e-09</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.002690467750653625</v>
+        <v>3.209053023311981e-09</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.003634867025539279</v>
+        <v>5.360002441889833e-10</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0004463897203095257</v>
+        <v>9.93321203068831e-10</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0001541467208880931</v>
+        <v>2.363146900385971e-10</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0007233851938508451</v>
+        <v>4.435999123586498e-09</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.000336262775817886</v>
+        <v>7.622238951121574e-11</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0013528389390558</v>
+        <v>3.406360749025339e-10</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.001098381704650819</v>
+        <v>3.915670898635426e-09</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.002023715060204268</v>
+        <v>3.861899688928361e-09</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.001553795766085386</v>
+        <v>1.402383209558877e-09</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.00280941603705287</v>
+        <v>4.822346966193436e-10</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.01017780601978302</v>
+        <v>5.787357260089721e-09</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.004567365162074566</v>
+        <v>2.233155660391617e-09</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.008055748417973518</v>
+        <v>7.571839821807202e-10</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.003789470298215747</v>
+        <v>4.53083259799314e-09</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.00284236017614603</v>
+        <v>4.513719620291567e-09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.01010951958596706</v>
+        <v>2.031640633504139e-09</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.565692506730556e-05</v>
+        <v>6.549166986502541e-09</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0050347950309515</v>
+        <v>1.986520059560348e-09</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.0005861823447048664</v>
+        <v>6.751426084861123e-10</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.009802058339118958</v>
+        <v>1.207771660460821e-10</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.005849417299032211</v>
+        <v>9.35195254569976e-10</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0006697001517750323</v>
+        <v>1.754752232407952e-09</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.002379861660301685</v>
+        <v>5.015026172117132e-09</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.00286557525396347</v>
+        <v>4.898683236831403e-09</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001818718737922609</v>
+        <v>9.136459921954554e-10</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.002118911826983094</v>
+        <v>4.851981594278243e-10</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0002208820078521967</v>
+        <v>1.181674225136931e-08</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0007806809735484421</v>
+        <v>2.682017719024543e-09</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0001546152634546161</v>
+        <v>3.687619543057963e-09</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.002757845912128687</v>
+        <v>2.242928287543577e-09</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.002350292634218931</v>
+        <v>1.43148382036884e-09</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01171121001243591</v>
+        <v>2.86016699213576e-09</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.003115449799224734</v>
+        <v>1.854152609226389e-09</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.001512174494564533</v>
+        <v>5.930703927958803e-09</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.009024842642247677</v>
+        <v>5.067286590332287e-10</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0002276686136610806</v>
+        <v>2.857749592521941e-10</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.001522470614872873</v>
+        <v>2.63776178677233e-09</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001757722115144134</v>
+        <v>3.430351114275254e-09</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.00280216708779335</v>
+        <v>9.751213170261508e-10</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.006085726898163557</v>
+        <v>1.54631285553819e-09</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.004833282437175512</v>
+        <v>3.040807605714235e-09</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.000223958253627643</v>
+        <v>3.666491554810136e-09</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.00563802057877183</v>
+        <v>6.130079999167037e-09</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.004860934801399708</v>
+        <v>1.317820297330741e-09</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.003930038306862116</v>
+        <v>1.385408232579266e-09</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0008367140544578433</v>
+        <v>1.024654139314407e-09</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.003571041859686375</v>
+        <v>2.294715972794847e-09</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.000116987299406901</v>
+        <v>1.604697263957178e-09</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.00207155873067677</v>
+        <v>4.932570463189734e-10</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001596234855242074</v>
+        <v>5.119685231314008e-10</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0009601297788321972</v>
+        <v>2.911265117866435e-10</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.000913260446395725</v>
+        <v>1.993387233056865e-09</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.001142277847975492</v>
+        <v>2.789196373864655e-10</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0007252913201227784</v>
+        <v>3.600701403705386e-10</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.004555470310151577</v>
+        <v>5.361679544790832e-09</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.006980228237807751</v>
+        <v>8.623606717605981e-09</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0008259770693257451</v>
+        <v>4.534957298574227e-09</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.009377509355545044</v>
+        <v>5.387839063786259e-09</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.01114512793719769</v>
+        <v>2.836958223895181e-09</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.000261485343798995</v>
+        <v>3.073856280622067e-09</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.004096312448382378</v>
+        <v>1.929152393387312e-09</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.002973274094983935</v>
+        <v>6.009036823684255e-09</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.004739210940897465</v>
+        <v>5.19131848619736e-09</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.00120483385398984</v>
+        <v>5.334124808520357e-10</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.00273717800155282</v>
+        <v>1.051784659367172e-09</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0006001935107633471</v>
+        <v>1.684019146352966e-09</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0008176038390956819</v>
+        <v>7.592929618382982e-10</v>
       </c>
       <c r="CZ5" t="n">
-        <v>6.05783388891723e-05</v>
+        <v>1.510977176710782e-10</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.001785708474926651</v>
+        <v>4.727156999173587e-10</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.001359961228445172</v>
+        <v>1.136061689166468e-09</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.002500410191714764</v>
+        <v>6.432880894635673e-10</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0002675238065421581</v>
+        <v>1.095966206676735e-09</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.005248290486633778</v>
+        <v>1.90309545899936e-09</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0002485329168848693</v>
+        <v>3.177079044291986e-09</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.00256530474871397</v>
+        <v>7.865475382118348e-09</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.009311666712164879</v>
+        <v>1.069296562405952e-08</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.00305444304831326</v>
+        <v>4.306589751479351e-09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0009621167555451393</v>
+        <v>3.632082856697139e-09</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.0008596015395596623</v>
+        <v>6.403042984715057e-09</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.004154433496296406</v>
+        <v>1.608299826649784e-09</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.006203212775290012</v>
+        <v>3.506213652748613e-10</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.00484640896320343</v>
+        <v>2.457909709097095e-10</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.002017597900703549</v>
+        <v>3.565543194028464e-09</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.002935330383479595</v>
+        <v>4.430704136915153e-10</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.001235917676240206</v>
+        <v>1.828634244027683e-09</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0007375174900516868</v>
+        <v>6.032653931953291e-09</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.00118799670599401</v>
+        <v>1.671747407172575e-09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.00066963373683393</v>
+        <v>5.249088275149916e-09</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.001244450686499476</v>
+        <v>2.74145528500469e-09</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.00514364056289196</v>
+        <v>2.823303368870711e-09</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0005753684090450406</v>
+        <v>4.808164977276874e-10</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.007664769887924194</v>
+        <v>9.022551594739525e-09</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.001230959547683597</v>
+        <v>1.367481350378341e-09</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.00424647843465209</v>
+        <v>4.671050657378828e-09</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.001252624671906233</v>
+        <v>5.250580414895012e-09</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.00230581290088594</v>
+        <v>3.148998395374747e-09</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.001436928287148476</v>
+        <v>4.302076028750434e-09</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.001826724386774004</v>
+        <v>3.138675097602572e-09</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.002666247077286243</v>
+        <v>7.541892443896359e-09</v>
       </c>
       <c r="EF5" t="n">
-        <v>1.530888948764186e-05</v>
+        <v>1.823330375572141e-09</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.002459352603182197</v>
+        <v>4.233904782324771e-09</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0007187866140156984</v>
+        <v>1.732042176350035e-09</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0007604434504173696</v>
+        <v>1.298197105370491e-09</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0007346588536165655</v>
+        <v>7.06581071430179e-10</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0008788767736405134</v>
+        <v>3.410199900244493e-09</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.00439628679305315</v>
+        <v>9.399422351563658e-10</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0004429516848176718</v>
+        <v>1.209905925447785e-10</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.0004766580241266638</v>
+        <v>1.189685849833921e-11</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.003550808411091566</v>
+        <v>1.310848873892212e-09</v>
       </c>
       <c r="EP5" t="n">
-        <v>9.578769095242023e-05</v>
+        <v>4.35567637513401e-10</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.001297101844102144</v>
+        <v>1.845341990325267e-09</v>
       </c>
       <c r="ER5" t="n">
-        <v>3.766556619666517e-05</v>
+        <v>1.711456421027435e-09</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0006663475651293993</v>
+        <v>1.858432630008622e-09</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.005961243994534016</v>
+        <v>3.933007253209553e-09</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.002193041145801544</v>
+        <v>3.981643903472332e-09</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0003231737646274269</v>
+        <v>2.887520444971869e-09</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.001788654248230159</v>
+        <v>3.112213264877539e-10</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.001931926002725959</v>
+        <v>1.840971375344225e-09</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.003444107482209802</v>
+        <v>2.068665461152364e-09</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.000162524709594436</v>
+        <v>1.580317432470224e-09</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.002345095621421933</v>
+        <v>1.420634387905295e-09</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0002010516764130443</v>
+        <v>6.402554042495012e-10</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0004658084362745285</v>
+        <v>6.151432696555048e-10</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0004326641792431474</v>
+        <v>1.367895685611131e-09</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.002439108677208424</v>
+        <v>6.971795363241995e-10</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0003664569812826812</v>
+        <v>1.292630558147323e-09</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.002697378862649202</v>
+        <v>4.54646897907196e-09</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.002705651801079512</v>
+        <v>5.879388087492998e-09</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.001278046634979546</v>
+        <v>1.945902994293647e-09</v>
       </c>
       <c r="FJ5" t="n">
-        <v>2.933328505605459e-05</v>
+        <v>7.946687752280468e-10</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0005357553018257022</v>
+        <v>6.944288477583882e-10</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.006142041180282831</v>
+        <v>2.342707139391109e-09</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0001372724073007703</v>
+        <v>2.124218356769347e-09</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.00301815546117723</v>
+        <v>4.420543042726877e-09</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.005656191147863865</v>
+        <v>8.68565930289833e-09</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001338417874649167</v>
+        <v>2.250976294249085e-09</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.003645888296887279</v>
+        <v>1.232467106149215e-08</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.003594424575567245</v>
+        <v>4.11216283247029e-10</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.001480945385992527</v>
+        <v>4.745539516903818e-09</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.002274092053994536</v>
+        <v>8.877195867285081e-09</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.002144434722140431</v>
+        <v>5.060166952119971e-09</v>
       </c>
       <c r="FV5" t="n">
-        <v>7.475932943634689e-05</v>
+        <v>7.833417470237691e-09</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.004400793462991714</v>
+        <v>1.424879592093475e-08</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.003508683992549777</v>
+        <v>5.859668306129606e-10</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.003768628230318427</v>
+        <v>6.763412052634976e-11</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0005015239585191011</v>
+        <v>4.7020543014753e-10</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.003965776413679123</v>
+        <v>4.366751404916158e-09</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.003078264882788062</v>
+        <v>5.64258550994623e-09</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.004025431349873543</v>
+        <v>5.136752800893873e-09</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.002733859233558178</v>
+        <v>3.486538613373114e-09</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.005450504366308451</v>
+        <v>1.174160990657924e-09</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.009752624668180943</v>
+        <v>4.277751486370107e-09</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.001951626967638731</v>
+        <v>2.028634149553454e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3844,1140 +3844,1140 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.001712451223284006</v>
+        <v>0.04376830160617828</v>
       </c>
       <c r="B7" t="n">
-        <v>0.05551702529191971</v>
+        <v>0.1058782711625099</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003317997790873051</v>
+        <v>0.1087574511766434</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03561419993638992</v>
+        <v>0.139778733253479</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008732371032238007</v>
+        <v>0.04601502418518066</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0004661672282963991</v>
+        <v>0.02949672751128674</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005130870267748833</v>
+        <v>0.1318042278289795</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008951134048402309</v>
+        <v>0.1442963778972626</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007986379787325859</v>
+        <v>0.1353447437286377</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002036442281678319</v>
+        <v>0.04448241740465164</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04515655338764191</v>
+        <v>0.1514201015233994</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00283030653372407</v>
+        <v>0.06059704348444939</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03208001330494881</v>
+        <v>0.1874988675117493</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01480635441839695</v>
+        <v>0.01892825216054916</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01045614387840033</v>
+        <v>0.03763752058148384</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0003362208371981978</v>
+        <v>0.04577012360095978</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.005479482933878899</v>
+        <v>0.2810549736022949</v>
       </c>
       <c r="R7" t="n">
-        <v>0.001253547379747033</v>
+        <v>0.1252629905939102</v>
       </c>
       <c r="S7" t="n">
-        <v>0.001196829602122307</v>
+        <v>0.02532141469419003</v>
       </c>
       <c r="T7" t="n">
-        <v>0.009715506806969643</v>
+        <v>0.09670688956975937</v>
       </c>
       <c r="U7" t="n">
-        <v>0.004223612137138844</v>
+        <v>0.09275579452514648</v>
       </c>
       <c r="V7" t="n">
-        <v>0.003020249772816896</v>
+        <v>0.003106418531388044</v>
       </c>
       <c r="W7" t="n">
-        <v>0.003887590486556292</v>
+        <v>0.02030257508158684</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009910805150866508</v>
+        <v>0.0615106038749218</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.005130209028720856</v>
+        <v>0.01240312308073044</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.004015122540295124</v>
+        <v>0.03759720548987389</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.006247510202229023</v>
+        <v>0.03186040744185448</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.003134108148515224</v>
+        <v>0.04024075344204903</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.008953223936259747</v>
+        <v>0.07474064826965332</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0003627233090810478</v>
+        <v>0.01093753799796104</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.002081290585920215</v>
+        <v>0.1965398788452148</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.002294933423399925</v>
+        <v>0.09145239740610123</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.005474292673170567</v>
+        <v>0.1667468398809433</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.003492803778499365</v>
+        <v>0.05194924026727676</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.004653371404856443</v>
+        <v>0.01366408541798592</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.000507187272887677</v>
+        <v>0.02032044716179371</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.001839381642639637</v>
+        <v>0.00100421067327261</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.003255453892052174</v>
+        <v>0.1560568511486053</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.0009045008919201791</v>
+        <v>0.1281237900257111</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.002002241555601358</v>
+        <v>0.03625335171818733</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.005844132974743843</v>
+        <v>0.09520821273326874</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.003704669419676065</v>
+        <v>0.02329297363758087</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.004928146488964558</v>
+        <v>0.01292309165000916</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.004217292182147503</v>
+        <v>0.0004501559305936098</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0001328879734501243</v>
+        <v>0.01852600090205669</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.005120197776705027</v>
+        <v>0.0001950515434145927</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0343066081404686</v>
+        <v>0.1996180862188339</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.003984069917351007</v>
+        <v>0.05580069497227669</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.006816944107413292</v>
+        <v>0.08987617492675781</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.001668954384513199</v>
+        <v>0.01506628002971411</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.005200459156185389</v>
+        <v>0.06826672703027725</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.002386830747127533</v>
+        <v>0.004589489195495844</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.009976780042052269</v>
+        <v>0.05862876027822495</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.00258116377517581</v>
+        <v>0.02670550346374512</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.00496617890894413</v>
+        <v>0.037265345454216</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.009713750332593918</v>
+        <v>0.233894020318985</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.01338137686252594</v>
+        <v>0.100458987057209</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.008055582642555237</v>
+        <v>0.09297914803028107</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.01712665520608425</v>
+        <v>0.1374724358320236</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.001677429885603487</v>
+        <v>0.0674111470580101</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.001644183183088899</v>
+        <v>0.03573887050151825</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.007552317809313536</v>
+        <v>0.15650574862957</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.645641406066716e-05</v>
+        <v>0.1509768217802048</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.007248692214488983</v>
+        <v>0.009668754413723946</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.003733418416231871</v>
+        <v>0.07824178040027618</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.002504392294213176</v>
+        <v>0.02619876898825169</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001316009787842631</v>
+        <v>0.03858675062656403</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.009139067493379116</v>
+        <v>0.05759922042489052</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.008512454107403755</v>
+        <v>0.08092428743839264</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0001768093788996339</v>
+        <v>0.0278388224542141</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.006808165460824966</v>
+        <v>0.07093650102615356</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.002976805903017521</v>
+        <v>0.01701104268431664</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.003186005167663097</v>
+        <v>0.03178836777806282</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.01784870959818363</v>
+        <v>0.2396233826875687</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.001244400627911091</v>
+        <v>0.06646064668893814</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.003405467141419649</v>
+        <v>0.05263547599315643</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.005701465997844934</v>
+        <v>0.001672714948654175</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.005100907757878304</v>
+        <v>0.07137441635131836</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.003026417223736644</v>
+        <v>0.01305823586881161</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.002875399310141802</v>
+        <v>0.1197133362293243</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.003099283669143915</v>
+        <v>0.0586102157831192</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.001596856745891273</v>
+        <v>0.008639493957161903</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.009809521026909351</v>
+        <v>0.03997617959976196</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0026205915492028</v>
+        <v>0.02692413330078125</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.004199174698442221</v>
+        <v>0.05315137282013893</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.002847715280950069</v>
+        <v>0.03474504873156548</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.001159585197456181</v>
+        <v>0.01536137238144875</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001683306763879955</v>
+        <v>0.02041239477694035</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0006619010819122195</v>
+        <v>0.03645648062229156</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.001899397931993008</v>
+        <v>0.02246250584721565</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.009589311666786671</v>
+        <v>0.04689531773328781</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.002770786872133613</v>
+        <v>0.0239685419946909</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.00121601449791342</v>
+        <v>0.06195803359150887</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.01066280249506235</v>
+        <v>0.171745240688324</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.008268781937658787</v>
+        <v>0.121704950928688</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.007352792657911777</v>
+        <v>0.026356291025877</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.009199545718729496</v>
+        <v>0.04140499234199524</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.009394527412950993</v>
+        <v>0.06703181564807892</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.000865189591422677</v>
+        <v>0.08030083030462265</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.001411815290339291</v>
+        <v>0.008933736011385918</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.008467532694339752</v>
+        <v>0.04201183840632439</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.004623329732567072</v>
+        <v>0.03308946639299393</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.006338294129818678</v>
+        <v>0.0585186742246151</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.003011378925293684</v>
+        <v>0.01335696503520012</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.002058736514300108</v>
+        <v>0.01009533740580082</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.002698918338865042</v>
+        <v>0.01636171154677868</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0006929205264896154</v>
+        <v>0.03725931420922279</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.001180613879114389</v>
+        <v>0.01644456572830677</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.002481469651684165</v>
+        <v>0.002618414349853992</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.01253604888916016</v>
+        <v>0.1101072803139687</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.004430346190929413</v>
+        <v>0.1288630068302155</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.01028701849281788</v>
+        <v>0.02734531834721565</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.007641813717782497</v>
+        <v>0.002357006072998047</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.002431318396702409</v>
+        <v>0.1070682108402252</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.003650238970294595</v>
+        <v>0.0505659207701683</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0007040286436676979</v>
+        <v>0.1125205755233765</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.003866566810756922</v>
+        <v>0.05280126631259918</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.0006286113057285547</v>
+        <v>0.02331487834453583</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.002445630030706525</v>
+        <v>0.01490484643727541</v>
       </c>
       <c r="DP7" t="n">
-        <v>8.020499080885202e-05</v>
+        <v>0.01436332985758781</v>
       </c>
       <c r="DQ7" t="n">
-        <v>7.582918624393642e-05</v>
+        <v>0.01773057505488396</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.006997537799179554</v>
+        <v>0.03520756214857101</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.004680521320551634</v>
+        <v>0.004621329717338085</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0013164347037673</v>
+        <v>0.01991313695907593</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.004402083810418844</v>
+        <v>0.05749880895018578</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.003161631990224123</v>
+        <v>0.09709365665912628</v>
       </c>
       <c r="DW7" t="n">
-        <v>1.792045077309012e-05</v>
+        <v>0.01185630820691586</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.001641349750570953</v>
+        <v>0.04582031816244125</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.006879191845655441</v>
+        <v>0.07283398509025574</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.003373092040419579</v>
+        <v>0.02685272507369518</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.001720996689982712</v>
+        <v>0.06428557634353638</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0006298954249359667</v>
+        <v>0.05636362731456757</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.002675341442227364</v>
+        <v>0.01624295674264431</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0007170896860770881</v>
+        <v>0.005289098713546991</v>
       </c>
       <c r="EE7" t="n">
-        <v>5.397840868681669e-05</v>
+        <v>0.06927234679460526</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.001758645754307508</v>
+        <v>0.02164579182863235</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.006987854838371277</v>
+        <v>0.02114110253751278</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.004475468769669533</v>
+        <v>0.02983720600605011</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.003838947741314769</v>
+        <v>0.04390855506062508</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.004836389794945717</v>
+        <v>0.02494066953659058</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.003097476437687874</v>
+        <v>0.06948703527450562</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.001913813641294837</v>
+        <v>0.0005376171320676804</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.000892376177944243</v>
+        <v>0.01807943917810917</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.001814081449992955</v>
+        <v>0.008171547204256058</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.001308454433456063</v>
+        <v>0.02330923452973366</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.007498554419726133</v>
+        <v>0.08386407047510147</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.005605580750852823</v>
+        <v>0.0115966759622097</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.003838609205558896</v>
+        <v>0.02272612042725086</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0003804285079240799</v>
+        <v>0.004314947873353958</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.005022427532821894</v>
+        <v>0.03148934245109558</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.005362623371183872</v>
+        <v>0.04404723644256592</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.00310002313926816</v>
+        <v>0.01452234759926796</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.001216457108967006</v>
+        <v>0.0444217175245285</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0003402102447580546</v>
+        <v>0.006042365916073322</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.00915110670030117</v>
+        <v>0.05071651190519333</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.002107943408191204</v>
+        <v>0.007464510854333639</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.005465697962790728</v>
+        <v>0.05672813579440117</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.00339048239402473</v>
+        <v>0.02604309841990471</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.00303193717263639</v>
+        <v>0.00197198148816824</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.002352969255298376</v>
+        <v>0.01538864616304636</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0002301300410181284</v>
+        <v>0.02514255791902542</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.002192257437855005</v>
+        <v>0.01948046684265137</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0005816424963995814</v>
+        <v>0.0146609228104353</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.00237417477183044</v>
+        <v>0.03801880031824112</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.005537247750908136</v>
+        <v>0.02283070981502533</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.003097842913120985</v>
+        <v>0.05656229704618454</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0005173486424610019</v>
+        <v>0.05568579211831093</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.001727911760099232</v>
+        <v>0.04681063443422318</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.000156732217874378</v>
+        <v>0.004122694954276085</v>
       </c>
       <c r="FN7" t="n">
-        <v>0.001049944199621677</v>
+        <v>0.00680401548743248</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.001024026423692703</v>
+        <v>0.08826464414596558</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0004925382672809064</v>
+        <v>0.05457223206758499</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.004472453147172928</v>
+        <v>0.05738472193479538</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.007826166227459908</v>
+        <v>0.04799042642116547</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.001124299364164472</v>
+        <v>0.0390801876783371</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001934168161824346</v>
+        <v>0.1366722732782364</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.002223839052021503</v>
+        <v>0.03402608633041382</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.00225441949442029</v>
+        <v>0.04516471549868584</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0008033763151615858</v>
+        <v>0.0002034939825534821</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.00637524202466011</v>
+        <v>0.01127584278583527</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.006072044838219881</v>
+        <v>0.002000625245273113</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.001911882311105728</v>
+        <v>0.1163877248764038</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.0008882062393240631</v>
+        <v>0.04187548533082008</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.001590659841895103</v>
+        <v>0.005878183990716934</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.001473621232435107</v>
+        <v>0.1075946688652039</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.009638539515435696</v>
+        <v>0.04047711938619614</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.01650968939065933</v>
+        <v>0.08443008363246918</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.001281450851820409</v>
+        <v>0.02926827222108841</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.005286006722599268</v>
+        <v>0.004773102700710297</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.000770552025642246</v>
+        <v>0.2918646931648254</v>
       </c>
       <c r="B8" t="n">
-        <v>0.005968571174889803</v>
+        <v>0.7352487444877625</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004607956798281521</v>
+        <v>0.1136990562081337</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003369116922840476</v>
+        <v>0.00698360800743103</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0008775252499617636</v>
+        <v>0.04304119199514389</v>
       </c>
       <c r="F8" t="n">
-        <v>0.003974397666752338</v>
+        <v>0.4341100454330444</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0001784896594472229</v>
+        <v>0.01039177179336548</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001381566049531102</v>
+        <v>0.09582322835922241</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002701282792259008</v>
+        <v>0.1556411385536194</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001729568350128829</v>
+        <v>0.1413607597351074</v>
       </c>
       <c r="K8" t="n">
-        <v>0.004632550291717052</v>
+        <v>0.9468108415603638</v>
       </c>
       <c r="L8" t="n">
-        <v>9.706163837108761e-05</v>
+        <v>0.05472858250141144</v>
       </c>
       <c r="M8" t="n">
-        <v>0.002971806796267629</v>
+        <v>0.1924274265766144</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0008494282374158502</v>
+        <v>0.204822450876236</v>
       </c>
       <c r="O8" t="n">
-        <v>0.004348634742200375</v>
+        <v>0.4795613288879395</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0002292415883857757</v>
+        <v>0.06119843944907188</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0002470288309268653</v>
+        <v>0.1114111617207527</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0002319524064660072</v>
+        <v>0.1325643658638</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0004497130867093801</v>
+        <v>0.02983781695365906</v>
       </c>
       <c r="T8" t="n">
-        <v>0.000851842574775219</v>
+        <v>0.270587682723999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0003688946599140763</v>
+        <v>0.01677405834197998</v>
       </c>
       <c r="V8" t="n">
-        <v>0.000571717566344887</v>
+        <v>0.2539186477661133</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002773168962448835</v>
+        <v>0.1257924437522888</v>
       </c>
       <c r="X8" t="n">
-        <v>0.000327616318827495</v>
+        <v>0.07910273224115372</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0007527851848863065</v>
+        <v>0.0499122329056263</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0004103438986930996</v>
+        <v>0.1798733323812485</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.000663748593069613</v>
+        <v>0.03505314514040947</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.665105370804667e-05</v>
+        <v>0.01051938813179731</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0006333448109216988</v>
+        <v>0.1502250880002975</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0001714517420623451</v>
+        <v>0.08534698188304901</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.498071651440114e-05</v>
+        <v>0.3066714704036713</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0003075880231335759</v>
+        <v>0.4575543403625488</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.000142938835779205</v>
+        <v>0.1274527907371521</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0005013957852497697</v>
+        <v>0.06193581223487854</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0003812020877376199</v>
+        <v>0.278546541929245</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0002418496587779373</v>
+        <v>0.006277252454310656</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0005611379747278988</v>
+        <v>0.00615614652633667</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0009357969393022358</v>
+        <v>0.3312493562698364</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.000293208722723648</v>
+        <v>0.05694105476140976</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0001711551449261606</v>
+        <v>0.08423890173435211</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0003124606155324727</v>
+        <v>0.1535726934671402</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0008001524256542325</v>
+        <v>0.1409933865070343</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0001058935740729794</v>
+        <v>0.1162465810775757</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0003496088902465999</v>
+        <v>0.2463291585445404</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0008411086746491492</v>
+        <v>0.08745569735765457</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0004574628255795687</v>
+        <v>0.09928329288959503</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.003819919191300869</v>
+        <v>1.005284547805786</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0003073289117310196</v>
+        <v>0.05804416537284851</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.0001001745768007822</v>
+        <v>0.01084601506590843</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.538460830692202e-05</v>
+        <v>0.1301701664924622</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.002250263700261712</v>
+        <v>0.5621464848518372</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.65750927105546e-05</v>
+        <v>0.02972757071256638</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001218306599184871</v>
+        <v>0.02377861551940441</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.001257407711818814</v>
+        <v>0.05903153866529465</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0009020776487886906</v>
+        <v>0.1109433099627495</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.001125702052377164</v>
+        <v>0.2874253392219543</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001622372772544622</v>
+        <v>0.05380357429385185</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.001059138565324247</v>
+        <v>0.1636679470539093</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001725678448565304</v>
+        <v>0.2950914204120636</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001122015062719584</v>
+        <v>0.006570564582943916</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.000321967585477978</v>
+        <v>0.1358357816934586</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001390494289807975</v>
+        <v>0.08663957566022873</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.019764209166169e-05</v>
+        <v>0.1049508824944496</v>
       </c>
       <c r="BL8" t="n">
-        <v>8.766798418946564e-05</v>
+        <v>0.1184681057929993</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0008521504933014512</v>
+        <v>0.03387625142931938</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0007782690227031708</v>
+        <v>0.01496965065598488</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0007580576930195093</v>
+        <v>0.07866257429122925</v>
       </c>
       <c r="BP8" t="n">
-        <v>7.452729187207296e-05</v>
+        <v>0.06015389412641525</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.141977842664346e-05</v>
+        <v>0.1176487132906914</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0007800947641953826</v>
+        <v>0.1096109747886658</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.0001019738701870665</v>
+        <v>0.01692210137844086</v>
       </c>
       <c r="BT8" t="n">
-        <v>7.59006361477077e-05</v>
+        <v>0.1045186072587967</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.000338937999913469</v>
+        <v>0.1007103323936462</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.00194436393212527</v>
+        <v>0.6876859664916992</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.0009020552970468998</v>
+        <v>0.001811109483242035</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0006910524680279195</v>
+        <v>0.1101874187588692</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.000568013230804354</v>
+        <v>0.0713898167014122</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0007537451456300914</v>
+        <v>0.3294286131858826</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0005808557034470141</v>
+        <v>0.09576969593763351</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0005904944846406579</v>
+        <v>0.09575997292995453</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0009326154831796885</v>
+        <v>0.037307508289814</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.998442116426304e-05</v>
+        <v>0.006872834637761116</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0009845332242548466</v>
+        <v>0.2756217122077942</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0007867696112953126</v>
+        <v>0.01919259876012802</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.000578657491132617</v>
+        <v>0.03862426429986954</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0004179140960332006</v>
+        <v>0.03723060339689255</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0007026444654911757</v>
+        <v>0.1395280361175537</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0003785433946177363</v>
+        <v>0.08317384123802185</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0002376710763201118</v>
+        <v>0.0237007811665535</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0005200766609050333</v>
+        <v>0.01527068763971329</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.0007940531941130757</v>
+        <v>0.2711411714553833</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0001352726685581729</v>
+        <v>0.4778795540332794</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.0003401360008865595</v>
+        <v>0.001252554357051849</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0007497876067645848</v>
+        <v>0.3726893365383148</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.0001129347219830379</v>
+        <v>0.3791870772838593</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.928478013724089e-06</v>
+        <v>0.3370223641395569</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0007479171617887914</v>
+        <v>0.06238213181495667</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0007319413125514984</v>
+        <v>0.003941751085221767</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0001093438040697947</v>
+        <v>0.07926422357559204</v>
       </c>
       <c r="CV8" t="n">
-        <v>5.553982191486284e-05</v>
+        <v>0.03422581031918526</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.0008893150370568037</v>
+        <v>0.2473026812076569</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0007562258397229016</v>
+        <v>0.01664904877543449</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0008598623680882156</v>
+        <v>0.05105447769165039</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.00037290298496373</v>
+        <v>0.03943554311990738</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0007778280414640903</v>
+        <v>0.1374886631965637</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.0003751181066036224</v>
+        <v>0.03362835198640823</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0006055086269043386</v>
+        <v>0.05482650920748711</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0003496996941976249</v>
+        <v>0.01551598403602839</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0002828605065587908</v>
+        <v>0.08646948635578156</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.001021860516630113</v>
+        <v>0.0201214998960495</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0002301351923961192</v>
+        <v>0.01474418491125107</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.002160317031666636</v>
+        <v>0.0403837077319622</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0003066898207180202</v>
+        <v>0.2742002904415131</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0001768382207956165</v>
+        <v>0.121162086725235</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0008513982756994665</v>
+        <v>0.1726710796356201</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0009089575614780188</v>
+        <v>0.1681337654590607</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0003127915551885962</v>
+        <v>0.007461324334144592</v>
       </c>
       <c r="DN8" t="n">
-        <v>3.139792897854932e-05</v>
+        <v>0.007093680091202259</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0001711990917101502</v>
+        <v>0.1246923729777336</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0005227990914136171</v>
+        <v>0.02214491181075573</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0005528955371119082</v>
+        <v>0.1515772640705109</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0003038592403754592</v>
+        <v>0.07236430794000626</v>
       </c>
       <c r="DS8" t="n">
-        <v>4.962440289091319e-05</v>
+        <v>0.01054327748715878</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0002676191506907344</v>
+        <v>0.0571899376809597</v>
       </c>
       <c r="DU8" t="n">
-        <v>4.387758963275701e-05</v>
+        <v>0.2336409389972687</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0008633123361505568</v>
+        <v>0.03770876675844193</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0001768039655871689</v>
+        <v>0.08984954655170441</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.0004491941654123366</v>
+        <v>0.07232046872377396</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0009313039481639862</v>
+        <v>0.05802979692816734</v>
       </c>
       <c r="DZ8" t="n">
-        <v>5.584931932389736e-05</v>
+        <v>0.03711695969104767</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0002582033048383892</v>
+        <v>0.03950647264719009</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0004186265578027815</v>
+        <v>0.1167185604572296</v>
       </c>
       <c r="EC8" t="n">
-        <v>4.004803486168385e-06</v>
+        <v>0.05615515634417534</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0002688472741283476</v>
+        <v>0.04072778299450874</v>
       </c>
       <c r="EE8" t="n">
-        <v>1.317714486503974e-05</v>
+        <v>0.04109103232622147</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0004141679673921317</v>
+        <v>0.004012316465377808</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0006314841448329389</v>
+        <v>0.0567905530333519</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0005620851297862828</v>
+        <v>0.03645846992731094</v>
       </c>
       <c r="EI8" t="n">
-        <v>8.132374205160886e-05</v>
+        <v>0.0530751496553421</v>
       </c>
       <c r="EJ8" t="n">
-        <v>7.864668441470712e-05</v>
+        <v>0.04573415219783783</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.00059619324747473</v>
+        <v>0.01730128563940525</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0006310882745310664</v>
+        <v>0.03599213808774948</v>
       </c>
       <c r="EM8" t="n">
-        <v>4.217106470605358e-05</v>
+        <v>0.03089857846498489</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0001417774619767442</v>
+        <v>0.01118718180805445</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.0001348709047306329</v>
+        <v>0.03690804168581963</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0003522846382111311</v>
+        <v>0.1039724498987198</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0008480310789309442</v>
+        <v>0.01220328081399202</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0004880840715486556</v>
+        <v>0.07455411553382874</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0005458757514134049</v>
+        <v>0.08698885887861252</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0006754539208486676</v>
+        <v>0.03566731512546539</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0007603303529322147</v>
+        <v>0.0005604401230812073</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.001021303585730493</v>
+        <v>0.02879343181848526</v>
       </c>
       <c r="EW8" t="n">
-        <v>2.411838067928329e-05</v>
+        <v>0.02405698411166668</v>
       </c>
       <c r="EX8" t="n">
-        <v>9.704244439490139e-05</v>
+        <v>0.01095420867204666</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0008353387238457799</v>
+        <v>0.2826709747314453</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0006068057264201343</v>
+        <v>0.01658184453845024</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0006930450326763093</v>
+        <v>0.0571490079164505</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0004475250898394734</v>
+        <v>0.006995073519647121</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0006286977441050112</v>
+        <v>0.1349179595708847</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0005982930306345224</v>
+        <v>0.104038804769516</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0003449803916737437</v>
+        <v>0.05152944475412369</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0005770737770944834</v>
+        <v>0.02399873547255993</v>
       </c>
       <c r="FG8" t="n">
-        <v>5.87866670684889e-05</v>
+        <v>0.04923136532306671</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0004573753103613853</v>
+        <v>0.2646760046482086</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.0007707474869675934</v>
+        <v>0.009839040227234364</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.0009020683355629444</v>
+        <v>0.2414785325527191</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0002935418742708862</v>
+        <v>0.08381107449531555</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.000569615513086319</v>
+        <v>0.2009323090314865</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0003509268572088331</v>
+        <v>0.1352716088294983</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0002410257002338767</v>
+        <v>0.3076517879962921</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0004382739425636828</v>
+        <v>0.01110333949327469</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0002819264191202819</v>
+        <v>0.09635688364505768</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.001007565879262984</v>
+        <v>0.4678171277046204</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0005233365227468312</v>
+        <v>0.01817277073860168</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.001126919407397509</v>
+        <v>0.2936374545097351</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.001097255502827466</v>
+        <v>0.1034714803099632</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0004352641990408301</v>
+        <v>0.1806329339742661</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0004989660228602588</v>
+        <v>0.1011332049965858</v>
       </c>
       <c r="FW8" t="n">
-        <v>0.0003849574131891131</v>
+        <v>0.03023298643529415</v>
       </c>
       <c r="FX8" t="n">
-        <v>7.011022535152733e-05</v>
+        <v>0.03442589938640594</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.001150390016846359</v>
+        <v>0.06645127385854721</v>
       </c>
       <c r="FZ8" t="n">
-        <v>4.74595399282407e-05</v>
+        <v>0.131905809044838</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0001501276419730857</v>
+        <v>0.003002915531396866</v>
       </c>
       <c r="GB8" t="n">
-        <v>6.375758675858378e-05</v>
+        <v>0.1194367557764053</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0002238859160570428</v>
+        <v>0.006438473239541054</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0005713164573535323</v>
+        <v>0.01511311996728182</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.002858526539057493</v>
+        <v>0.1202620267868042</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0002044062275672331</v>
+        <v>0.1450059413909912</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0004865959053859115</v>
+        <v>0.1392791420221329</v>
       </c>
     </row>
     <row r="9">
@@ -5551,2278 +5551,2278 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.6638014316558838</v>
+        <v>4.79147165606264e-05</v>
       </c>
       <c r="B10" t="n">
-        <v>1.2353355884552</v>
+        <v>1.073866587830707e-05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.131486102938652</v>
+        <v>6.5164622355951e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2079101353883743</v>
+        <v>1.18146745080594e-05</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2985281944274902</v>
+        <v>6.907097849762067e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2510347068309784</v>
+        <v>1.237738251802512e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1080858558416367</v>
+        <v>5.769538984168321e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.486358761787415</v>
+        <v>3.979148459620774e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2078614085912704</v>
+        <v>3.48240282619372e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5545161366462708</v>
+        <v>9.162101923720911e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8470445275306702</v>
+        <v>5.994499588268809e-06</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05553857982158661</v>
+        <v>1.252039328392129e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>0.09620147943496704</v>
+        <v>6.428372580558062e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5094627737998962</v>
+        <v>0.000131103879539296</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2175142168998718</v>
+        <v>1.533056456537452e-05</v>
       </c>
       <c r="P10" t="n">
-        <v>0.01761463284492493</v>
+        <v>0.0001286627230001613</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.711702227592468</v>
+        <v>0.0001039771159412339</v>
       </c>
       <c r="R10" t="n">
-        <v>0.440434068441391</v>
+        <v>5.683243944076821e-05</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1572821885347366</v>
+        <v>5.623556353384629e-05</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3289788961410522</v>
+        <v>5.432661419035867e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0337803065776825</v>
+        <v>1.957080166903324e-05</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1415750682353973</v>
+        <v>2.19438206841005e-05</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3380496203899384</v>
+        <v>3.654441024991684e-05</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3104378879070282</v>
+        <v>2.585755464679096e-05</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.03666971251368523</v>
+        <v>1.164406967291143e-05</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.2314796447753906</v>
+        <v>5.687206794391386e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04269574582576752</v>
+        <v>2.397513526375405e-05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.06493633240461349</v>
+        <v>1.903847442008555e-05</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.4368309676647186</v>
+        <v>1.082416474673664e-05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0558655709028244</v>
+        <v>4.3939860915998e-05</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1849061846733093</v>
+        <v>3.839042256004177e-05</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.2306345254182816</v>
+        <v>5.144911847310141e-05</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.02106809243559837</v>
+        <v>3.910569284926169e-05</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.1186276525259018</v>
+        <v>1.207196692121215e-05</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.4300580620765686</v>
+        <v>2.057462734228466e-05</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.05333126336336136</v>
+        <v>1.280113974644337e-05</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.3881820440292358</v>
+        <v>6.093300180509686e-05</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.07386790215969086</v>
+        <v>4.584478665492497e-05</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.03234489262104034</v>
+        <v>7.996932254172862e-06</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.007018239237368107</v>
+        <v>2.384554318268783e-05</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.0499989315867424</v>
+        <v>2.758760820142925e-05</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.02937968634068966</v>
+        <v>8.892129699233919e-06</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.1326632797718048</v>
+        <v>6.47078559268266e-06</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.2419698536396027</v>
+        <v>1.989214251807425e-05</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.1424376964569092</v>
+        <v>1.636817250982858e-05</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.2551524937152863</v>
+        <v>0.0001270860229851678</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.503349542617798</v>
+        <v>0.0001486564287915826</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.1344801187515259</v>
+        <v>3.187471520504914e-05</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.4541931748390198</v>
+        <v>2.103830593114253e-05</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.5768639445304871</v>
+        <v>8.256351065938361e-06</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.09108079224824905</v>
+        <v>2.966369720525108e-06</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.3138200640678406</v>
+        <v>2.080437661788892e-05</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.09312114119529724</v>
+        <v>1.892689579108264e-05</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.1467163860797882</v>
+        <v>3.563705831766129e-05</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.3602942228317261</v>
+        <v>1.049438105837908e-05</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.2222508639097214</v>
+        <v>9.938536095432937e-05</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.4930488169193268</v>
+        <v>9.326466170023195e-06</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.4205927550792694</v>
+        <v>3.747154551092535e-05</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.5764857530593872</v>
+        <v>0.0001410005206707865</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.04356098175048828</v>
+        <v>1.987311225093435e-05</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.318427175283432</v>
+        <v>7.263905717991292e-05</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.8644375801086426</v>
+        <v>4.496063866099576e-06</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.198231965303421</v>
+        <v>1.372838232782669e-05</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.02568998374044895</v>
+        <v>1.192048694065306e-05</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.942331075668335</v>
+        <v>8.226801583077759e-05</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.1183120906352997</v>
+        <v>2.698786920518614e-05</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.845369815826416</v>
+        <v>2.782464071060531e-05</v>
       </c>
       <c r="BP10" t="n">
-        <v>1.031805396080017</v>
+        <v>8.615637489128858e-05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.2344644218683243</v>
+        <v>9.066868369700387e-05</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.02442243695259094</v>
+        <v>6.251326340134256e-06</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.3962807953357697</v>
+        <v>2.526571370253805e-05</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.1065912470221519</v>
+        <v>4.475613877730211e-06</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.1126942485570908</v>
+        <v>0.0001122558460338041</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.6429307460784912</v>
+        <v>0.000118693416879978</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.2330402880907059</v>
+        <v>1.853108187788166e-05</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.1089700683951378</v>
+        <v>2.53918296948541e-05</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.4119422733783722</v>
+        <v>5.64529727853369e-06</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0928306058049202</v>
+        <v>7.88234501669649e-06</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.5128641128540039</v>
+        <v>3.594785084715113e-05</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.07915857434272766</v>
+        <v>3.39264988724608e-05</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.1660268902778625</v>
+        <v>2.613954620755976e-06</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.05134830623865128</v>
+        <v>2.999991374963429e-05</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.2752035558223724</v>
+        <v>1.835531975302729e-06</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.1233749911189079</v>
+        <v>6.937851139809936e-06</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.06314902007579803</v>
+        <v>1.569068990647793e-05</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0405261367559433</v>
+        <v>2.656837932590861e-05</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.2197877913713455</v>
+        <v>1.411197263223585e-05</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.01312040537595749</v>
+        <v>2.027074151556008e-05</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.3045412600040436</v>
+        <v>1.0627670235408e-05</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.07084982097148895</v>
+        <v>1.462012914998922e-05</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.6791375279426575</v>
+        <v>3.818573532043956e-05</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.7862738370895386</v>
+        <v>6.817866233177483e-05</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.05424945801496506</v>
+        <v>9.043187674251385e-07</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.3424024283885956</v>
+        <v>7.515056495321915e-06</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.7879053950309753</v>
+        <v>8.229145169025287e-05</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.06060314923524857</v>
+        <v>1.623869320610538e-05</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.04264715313911438</v>
+        <v>6.176104216137901e-05</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.2914796471595764</v>
+        <v>5.815377789986087e-06</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.06918765604496002</v>
+        <v>4.665888991439715e-05</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.01343058608472347</v>
+        <v>1.949795841937885e-05</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.1843138188123703</v>
+        <v>5.231531758909114e-06</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.1571419239044189</v>
+        <v>1.230441739608068e-05</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.2089582979679108</v>
+        <v>1.450393301638542e-05</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.00968928262591362</v>
+        <v>2.069450783892535e-05</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.2031300812959671</v>
+        <v>1.10563241833006e-05</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.04875680059194565</v>
+        <v>1.881202297226992e-05</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.1688516139984131</v>
+        <v>2.81384855043143e-05</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.008813595399260521</v>
+        <v>1.627407255000435e-05</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.6822954416275024</v>
+        <v>2.349737223994453e-05</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.9643968939781189</v>
+        <v>1.24034340842627e-06</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.05634043738245964</v>
+        <v>6.278651198954321e-08</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.6012055277824402</v>
+        <v>5.668022640747949e-05</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.04603531956672668</v>
+        <v>6.260211375774816e-05</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.004166989121586084</v>
+        <v>5.510785558726639e-05</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.4092905819416046</v>
+        <v>1.726764821796678e-06</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.04836790636181831</v>
+        <v>6.065301931812428e-05</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.1004059612751007</v>
+        <v>0.0001442698849132285</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.3762313425540924</v>
+        <v>6.963949999772012e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.229171097278595</v>
+        <v>9.188656804326456e-06</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.207751676440239</v>
+        <v>9.15493103548215e-07</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.1293793916702271</v>
+        <v>3.695303530548699e-05</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.1089334115386009</v>
+        <v>2.310565287189092e-05</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.07623948901891708</v>
+        <v>0.0001078675704775378</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1324042528867722</v>
+        <v>4.424476173880976e-06</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.1434755772352219</v>
+        <v>4.818725574295968e-05</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.1416294127702713</v>
+        <v>7.608507075929083e-06</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.1781472563743591</v>
+        <v>1.674507984716911e-05</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.01867571845650673</v>
+        <v>4.183849341643509e-06</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.1019336730241776</v>
+        <v>2.116559699061327e-05</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.4254487454891205</v>
+        <v>2.969807974295691e-05</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.101734034717083</v>
+        <v>9.869741916190833e-05</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.1688350290060043</v>
+        <v>3.594330701162107e-05</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.1740557551383972</v>
+        <v>3.452454984653741e-05</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.2701775431632996</v>
+        <v>1.877132308436558e-05</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.1430870741605759</v>
+        <v>3.497907528071664e-07</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.1427442729473114</v>
+        <v>1.393672027916182e-05</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.04013865441083908</v>
+        <v>2.44431084865937e-05</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.02556898817420006</v>
+        <v>3.36532793880906e-05</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.4102564454078674</v>
+        <v>9.49648892856203e-06</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04817326739430428</v>
+        <v>1.050240643962752e-05</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.1377459913492203</v>
+        <v>9.188298463413958e-06</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0585709847509861</v>
+        <v>3.938354711863212e-05</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.2946288585662842</v>
+        <v>1.294985304411966e-05</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.06204751878976822</v>
+        <v>8.981978680822067e-06</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.2755288481712341</v>
+        <v>1.267519110115245e-05</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0816301628947258</v>
+        <v>3.005257894983515e-05</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.1720314472913742</v>
+        <v>2.895045690820552e-05</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.001258097589015961</v>
+        <v>1.805815554689616e-05</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.2482740879058838</v>
+        <v>2.092006434395444e-05</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.1549697369337082</v>
+        <v>3.480068335193209e-05</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.1781202852725983</v>
+        <v>1.668776894803159e-05</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.02250642701983452</v>
+        <v>3.223690873710439e-05</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.1067533642053604</v>
+        <v>2.974837479996495e-05</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.02998455427587032</v>
+        <v>2.922993735410273e-05</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1681115031242371</v>
+        <v>6.041573669790523e-06</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0836583748459816</v>
+        <v>9.490980119153392e-06</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.1104254126548767</v>
+        <v>2.059822872979566e-05</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.04518879950046539</v>
+        <v>1.700398752291221e-05</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.2156047821044922</v>
+        <v>8.19037995825056e-06</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.1011290475726128</v>
+        <v>2.12057821045164e-05</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.3066435158252716</v>
+        <v>3.120717519777827e-05</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.04769366979598999</v>
+        <v>2.70649488811614e-05</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.2520991563796997</v>
+        <v>5.447351213661022e-06</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.07199016213417053</v>
+        <v>2.173663051507901e-05</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.1351915299892426</v>
+        <v>5.685819633072242e-05</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.1257397830486298</v>
+        <v>6.173632573336363e-05</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.28151535987854</v>
+        <v>2.296517413924448e-05</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.01195625960826874</v>
+        <v>7.782053216942586e-06</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.1135232448577881</v>
+        <v>8.998489647638053e-06</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.02116311155259609</v>
+        <v>2.111630237777717e-05</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.08935742825269699</v>
+        <v>3.636911424109712e-05</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.2317067533731461</v>
+        <v>8.901246474124491e-05</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.111503429710865</v>
+        <v>9.429904457647353e-05</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.203255295753479</v>
+        <v>0.0001605759025551379</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.6663557887077332</v>
+        <v>9.134881111094728e-05</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.3714026808738708</v>
+        <v>8.505224832333624e-05</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0947117805480957</v>
+        <v>1.165474168374203e-05</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.3654701411724091</v>
+        <v>2.799341700665536e-06</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.1735096275806427</v>
+        <v>7.989910955075175e-08</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.131647065281868</v>
+        <v>4.437814277480356e-05</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.226314976811409</v>
+        <v>4.281711153453216e-05</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.4960937798023224</v>
+        <v>5.223009793553501e-05</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.06160632520914078</v>
+        <v>1.859369149315171e-05</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.3634620010852814</v>
+        <v>7.999975059647113e-05</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.2613537609577179</v>
+        <v>9.240977669833228e-05</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.1324509233236313</v>
+        <v>7.765821465000045e-06</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.2019974887371063</v>
+        <v>1.199847247335128e-05</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.403831958770752</v>
+        <v>3.029916479135863e-05</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.1235048323869705</v>
+        <v>1.271628207177855e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1073690503835678</v>
+        <v>0.6378781795501709</v>
       </c>
       <c r="B11" t="n">
-        <v>0.346339613199234</v>
+        <v>0.5226889252662659</v>
       </c>
       <c r="C11" t="n">
-        <v>0.02318480052053928</v>
+        <v>0.2668024301528931</v>
       </c>
       <c r="D11" t="n">
-        <v>0.009361162781715393</v>
+        <v>0.05274830758571625</v>
       </c>
       <c r="E11" t="n">
-        <v>0.009961176663637161</v>
+        <v>0.2288859635591507</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1010008007287979</v>
+        <v>0.02037976495921612</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06907206773757935</v>
+        <v>0.1459841132164001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.08202123641967773</v>
+        <v>0.1161520928144455</v>
       </c>
       <c r="I11" t="n">
-        <v>0.04637730866670609</v>
+        <v>0.2164157032966614</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08386261761188507</v>
+        <v>0.360845685005188</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2731560468673706</v>
+        <v>0.8947610855102539</v>
       </c>
       <c r="L11" t="n">
-        <v>0.02547243610024452</v>
+        <v>0.03636034578084946</v>
       </c>
       <c r="M11" t="n">
-        <v>0.08625693619251251</v>
+        <v>0.2480622977018356</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2250356078147888</v>
+        <v>0.2668264508247375</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1682782024145126</v>
+        <v>0.1320862621068954</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1367961466312408</v>
+        <v>0.02536721527576447</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.273462176322937</v>
+        <v>0.4747474789619446</v>
       </c>
       <c r="R11" t="n">
-        <v>0.06488793343305588</v>
+        <v>0.3062368929386139</v>
       </c>
       <c r="S11" t="n">
-        <v>0.03517706692218781</v>
+        <v>0.05983512848615646</v>
       </c>
       <c r="T11" t="n">
-        <v>0.196549579501152</v>
+        <v>0.2308183312416077</v>
       </c>
       <c r="U11" t="n">
-        <v>0.05040950700640678</v>
+        <v>0.2764254808425903</v>
       </c>
       <c r="V11" t="n">
-        <v>0.02288753539323807</v>
+        <v>0.09981240332126617</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1652916967868805</v>
+        <v>0.1583285182714462</v>
       </c>
       <c r="X11" t="n">
-        <v>0.08143265545368195</v>
+        <v>0.1977542638778687</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.03488921374082565</v>
+        <v>0.04181734099984169</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.02231293730437756</v>
+        <v>0.0725313127040863</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02939659543335438</v>
+        <v>0.003095801919698715</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.001175613608211279</v>
+        <v>0.3113919794559479</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.09467174857854843</v>
+        <v>0.3553056120872498</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.04747354984283447</v>
+        <v>0.2844686210155487</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.1315018385648727</v>
+        <v>0.1812978833913803</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.08476722985506058</v>
+        <v>0.2386552691459656</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.1410119533538818</v>
+        <v>0.133332759141922</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.1175428032875061</v>
+        <v>0.04607679694890976</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0574151948094368</v>
+        <v>0.3016940057277679</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.000393726397305727</v>
+        <v>0.02001095935702324</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.1065556481480598</v>
+        <v>0.009375065565109253</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.09353291988372803</v>
+        <v>0.3766795694828033</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.02986415103077888</v>
+        <v>0.1589976251125336</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.06006063520908356</v>
+        <v>0.009138509631156921</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.05550927296280861</v>
+        <v>0.01026827096939087</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.1021693572402</v>
+        <v>0.1510885506868362</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.1058583855628967</v>
+        <v>0.03780009597539902</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.09215715527534485</v>
+        <v>0.2508286237716675</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.03552202507853508</v>
+        <v>0.02146424725651741</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.1924834549427032</v>
+        <v>0.1138317734003067</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.3739234805107117</v>
+        <v>0.7549062967300415</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.04587886109948158</v>
+        <v>0.2126765549182892</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.04352736100554466</v>
+        <v>0.08921407163143158</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.2893241047859192</v>
+        <v>0.01156732812523842</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.002582930028438568</v>
+        <v>0.0734734907746315</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.01001347042620182</v>
+        <v>0.04198461771011353</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.1018032133579254</v>
+        <v>0.04872016236186028</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.08290362358093262</v>
+        <v>0.06803853064775467</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.1070578768849373</v>
+        <v>0.7102152109146118</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.02411236986517906</v>
+        <v>0.2484486848115921</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.04458180814981461</v>
+        <v>0.3024831414222717</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.03671650588512421</v>
+        <v>0.03434935957193375</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.2135571986436844</v>
+        <v>0.5416443347930908</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.06660464406013489</v>
+        <v>0.05141105130314827</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.06741639971733093</v>
+        <v>0.0321897454559803</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.2027902454137802</v>
+        <v>0.2056525051593781</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.07386676222085953</v>
+        <v>0.1842243820428848</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.03009234368801117</v>
+        <v>0.1197806671261787</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1287059932947159</v>
+        <v>0.388425350189209</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.01752747595310211</v>
+        <v>0.09121549129486084</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.2163684964179993</v>
+        <v>0.05027511715888977</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.34635129570961</v>
+        <v>0.2366995811462402</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.08544362336397171</v>
+        <v>0.3473303318023682</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.01165451947599649</v>
+        <v>0.2144496440887451</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.176150381565094</v>
+        <v>0.01690725237131119</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0999637097120285</v>
+        <v>0.05238321796059608</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.09473149478435516</v>
+        <v>0.2105088382959366</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2007409781217575</v>
+        <v>0.8253782987594604</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.007076487876474857</v>
+        <v>0.3396323323249817</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.05398904904723167</v>
+        <v>0.1190005540847778</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.09734389930963516</v>
+        <v>0.002521550515666604</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.02998557314276695</v>
+        <v>0.06438228487968445</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.1260780990123749</v>
+        <v>0.19418103992939</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.04988543689250946</v>
+        <v>0.07901115715503693</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.006856180727481842</v>
+        <v>0.07949936389923096</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.003105447627604008</v>
+        <v>0.1179643198847771</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.07095640152692795</v>
+        <v>0.2400992214679718</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.01827999949455261</v>
+        <v>0.1485674977302551</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.03323822468519211</v>
+        <v>0.02223202027380466</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.02459714561700821</v>
+        <v>0.02946431934833527</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.01300865784287453</v>
+        <v>0.05324677377939224</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.00434052012860775</v>
+        <v>8.631683886051178e-05</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.001534496899694204</v>
+        <v>0.04034805670380592</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.01332314312458038</v>
+        <v>0.04790285602211952</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.1778358966112137</v>
+        <v>0.1443556100130081</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.1245193481445312</v>
+        <v>0.6050664782524109</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.01516254153102636</v>
+        <v>0.06946994364261627</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0594259649515152</v>
+        <v>0.1986723840236664</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.2779352068901062</v>
+        <v>0.222911149263382</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.0193987675011158</v>
+        <v>0.2169771939516068</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.09339445829391479</v>
+        <v>0.02933021821081638</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.02432887628674507</v>
+        <v>0.1420691907405853</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.06026003882288933</v>
+        <v>0.0198964811861515</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.01542760245501995</v>
+        <v>0.05919140949845314</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.07769418507814407</v>
+        <v>0.2250449955463409</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.01414863578975201</v>
+        <v>0.1441084295511246</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.05546914041042328</v>
+        <v>0.07632531225681305</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.009231838397681713</v>
+        <v>0.03221798688173294</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02541167661547661</v>
+        <v>0.005082886666059494</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.02153138630092144</v>
+        <v>0.0187042597681284</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0257538054138422</v>
+        <v>0.01496246643364429</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.01026903092861176</v>
+        <v>0.03362103551626205</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.2201390266418457</v>
+        <v>0.040640689432621</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.4430433213710785</v>
+        <v>0.8092502951622009</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.0186298806220293</v>
+        <v>0.123575434088707</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.02965892851352692</v>
+        <v>0.2455731779336929</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.02999074012041092</v>
+        <v>0.08173101395368576</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.1799720227718353</v>
+        <v>0.09743983298540115</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.1328354626893997</v>
+        <v>0.01615229062736034</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.05654424801468849</v>
+        <v>0.0870090126991272</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.1317484080791473</v>
+        <v>0.04522688686847687</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.09238102287054062</v>
+        <v>0.05134331807494164</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.1426840424537659</v>
+        <v>0.07037284225225449</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.02400673553347588</v>
+        <v>0.02847264334559441</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.09991795569658279</v>
+        <v>0.005358204245567322</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.07182853668928146</v>
+        <v>0.160456970334053</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.001239093020558357</v>
+        <v>0.09965251386165619</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.09704578667879105</v>
+        <v>0.03177756443619728</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.01949787139892578</v>
+        <v>0.09685511887073517</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.06733224540948868</v>
+        <v>0.004800314083695412</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.04632854461669922</v>
+        <v>0.3205365240573883</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.07725917547941208</v>
+        <v>0.3916730284690857</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.06600959599018097</v>
+        <v>0.1675716489553452</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.1268309354782104</v>
+        <v>0.06726273149251938</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.06281750649213791</v>
+        <v>0.193612739443779</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.04614744707942009</v>
+        <v>0.1281283050775528</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.08221111446619034</v>
+        <v>0.05257865414023399</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.05367451533675194</v>
+        <v>0.1269990801811218</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.06244016066193581</v>
+        <v>0.1471916139125824</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.07349630445241928</v>
+        <v>0.09398577362298965</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.1197163164615631</v>
+        <v>0.03309937566518784</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.01581370644271374</v>
+        <v>0.06827777624130249</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.05349035561084747</v>
+        <v>0.05305355042219162</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.030933678150177</v>
+        <v>0.1028165519237518</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.04570693895220757</v>
+        <v>0.05414779484272003</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.0519094280898571</v>
+        <v>0.01369627937674522</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.02660638839006424</v>
+        <v>0.1096016019582748</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.01976381428539753</v>
+        <v>0.006721490062773228</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.05085606873035431</v>
+        <v>0.006146200932562351</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.003630812279880047</v>
+        <v>0.1592925786972046</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.003642316441982985</v>
+        <v>0.01127037405967712</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.009702246636152267</v>
+        <v>0.1068685054779053</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.01841798610985279</v>
+        <v>0.2403308749198914</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.04151736572384834</v>
+        <v>0.1267283260822296</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.03317861258983612</v>
+        <v>0.1209893822669983</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.03374951705336571</v>
+        <v>0.05431581661105156</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.04733726009726524</v>
+        <v>0.05518738180398941</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.008746309205889702</v>
+        <v>0.08628027141094208</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0611720085144043</v>
+        <v>0.2990465760231018</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.007847069762647152</v>
+        <v>0.1410570293664932</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.03338529914617538</v>
+        <v>0.01431247778236866</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.03802549466490746</v>
+        <v>0.05025685951113701</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0124257942661643</v>
+        <v>0.01813381165266037</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.005152331665158272</v>
+        <v>0.01340340636670589</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.02248391695320606</v>
+        <v>0.04816366732120514</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.001684804330579937</v>
+        <v>0.05096159130334854</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.1277180016040802</v>
+        <v>0.1075152084231377</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.06589893996715546</v>
+        <v>0.04427033662796021</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.02827341482043266</v>
+        <v>0.05804502218961716</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.1085199862718582</v>
+        <v>0.2242911756038666</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.03536390513181686</v>
+        <v>0.07057757675647736</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0117553872987628</v>
+        <v>0.1945049166679382</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.00466054305434227</v>
+        <v>0.09460128843784332</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.04934792220592499</v>
+        <v>0.07104605436325073</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.04594143852591515</v>
+        <v>0.01349765434861183</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.04356934502720833</v>
+        <v>0.05939357727766037</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.05265555530786514</v>
+        <v>0.1759568452835083</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.06109566986560822</v>
+        <v>0.0713997408747673</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.1876389384269714</v>
+        <v>0.2484779804944992</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.1428343504667282</v>
+        <v>0.8818115592002869</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.01631923019886017</v>
+        <v>0.1089705675840378</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.02339364215731621</v>
+        <v>0.01879135519266129</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.02682185173034668</v>
+        <v>0.01443291455507278</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.06171915307641029</v>
+        <v>0.1334373205900192</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.01836609281599522</v>
+        <v>0.1088477373123169</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.1492711454629898</v>
+        <v>0.2647822201251984</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.05328135192394257</v>
+        <v>0.01442160457372665</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.2267229110002518</v>
+        <v>0.0266974326223135</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.2676382958889008</v>
+        <v>0.2151717245578766</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.07783018797636032</v>
+        <v>0.002909751608967781</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.1394986063241959</v>
+        <v>0.1530998945236206</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.2408899068832397</v>
+        <v>0.09633162617683411</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.02924237214028835</v>
+        <v>0.08906132727861404</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.004335778765380383</v>
+        <v>0.167400598526001</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1669000834226608</v>
+        <v>0.03299322724342346</v>
       </c>
       <c r="C12" t="n">
-        <v>0.01519213151186705</v>
+        <v>0.04230218380689621</v>
       </c>
       <c r="D12" t="n">
-        <v>0.04427432268857956</v>
+        <v>0.1126633882522583</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03968667611479759</v>
+        <v>0.1818549335002899</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04145682975649834</v>
+        <v>0.003738891333341599</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07402537763118744</v>
+        <v>0.2958007752895355</v>
       </c>
       <c r="H12" t="n">
-        <v>0.005588884465396404</v>
+        <v>0.327224999666214</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01241823099553585</v>
+        <v>0.1432017385959625</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02033091336488724</v>
+        <v>0.1424276977777481</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1193558648228645</v>
+        <v>0.1722819805145264</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006157295778393745</v>
+        <v>0.2253500521183014</v>
       </c>
       <c r="M12" t="n">
-        <v>0.08217861503362656</v>
+        <v>0.1465660184621811</v>
       </c>
       <c r="N12" t="n">
-        <v>0.04932829737663269</v>
+        <v>0.1281826794147491</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05120019987225533</v>
+        <v>0.2130565196275711</v>
       </c>
       <c r="P12" t="n">
-        <v>0.06643769890069962</v>
+        <v>0.3951491415500641</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02543927915394306</v>
+        <v>0.3794947266578674</v>
       </c>
       <c r="R12" t="n">
-        <v>0.005960079375654459</v>
+        <v>0.02815429493784904</v>
       </c>
       <c r="S12" t="n">
-        <v>0.02244327403604984</v>
+        <v>0.06975766271352768</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04580749943852425</v>
+        <v>0.04758305847644806</v>
       </c>
       <c r="U12" t="n">
-        <v>0.002266950439661741</v>
+        <v>0.08160436153411865</v>
       </c>
       <c r="V12" t="n">
-        <v>0.001063859090209007</v>
+        <v>0.001562351360917091</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04235599935054779</v>
+        <v>0.01491638831794262</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03222987428307533</v>
+        <v>0.02268098667263985</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.001326830009929836</v>
+        <v>0.07068726420402527</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.004435450304299593</v>
+        <v>0.06077727302908897</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.01542688626796007</v>
+        <v>0.121895506978035</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.0161537192761898</v>
+        <v>0.1552413403987885</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.03859755396842957</v>
+        <v>0.1542207896709442</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.002770435996353626</v>
+        <v>0.1984144151210785</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.003386207390576601</v>
+        <v>0.03454522788524628</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.002396240830421448</v>
+        <v>0.2352438122034073</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.008686551824212074</v>
+        <v>0.1668405532836914</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0007657431997358799</v>
+        <v>0.01048235222697258</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.004424836952239275</v>
+        <v>0.006264633499085903</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.01537936553359032</v>
+        <v>0.02873284183442593</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.01999026536941528</v>
+        <v>0.09528522938489914</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02181441523134708</v>
+        <v>0.2193031311035156</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.0007078601629473269</v>
+        <v>0.09195394814014435</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.01759385131299496</v>
+        <v>0.03851549327373505</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.009334308095276356</v>
+        <v>0.08385553956031799</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.006601404864341021</v>
+        <v>0.06343045085668564</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.01229801587760448</v>
+        <v>0.06665132939815521</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.004076240584254265</v>
+        <v>0.02586330845952034</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.008237873204052448</v>
+        <v>0.06988917291164398</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.04879670590162277</v>
+        <v>0.1850603222846985</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1499427706003189</v>
+        <v>0.3754450976848602</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.0001844220678322017</v>
+        <v>0.1271674335002899</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.04057848453521729</v>
+        <v>0.1193005442619324</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.009403831325471401</v>
+        <v>0.04444001987576485</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.02160320617258549</v>
+        <v>0.1833188831806183</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.02064731530845165</v>
+        <v>0.05283675715327263</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.02041184343397617</v>
+        <v>0.1461359262466431</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.01041141990572214</v>
+        <v>0.03178576752543449</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.01509539410471916</v>
+        <v>0.01373912394046783</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.03096080757677555</v>
+        <v>0.3212704658508301</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.0490340031683445</v>
+        <v>0.06902772188186646</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.03899641707539558</v>
+        <v>0.0301707535982132</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.04222442582249641</v>
+        <v>0.2871363162994385</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.02414114214479923</v>
+        <v>0.04003162682056427</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.0306980274617672</v>
+        <v>0.1401609778404236</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.03436363488435745</v>
+        <v>0.1842119842767715</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.0077357217669487</v>
+        <v>0.1315071731805801</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.006798411719501019</v>
+        <v>0.04856865108013153</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.04735756292939186</v>
+        <v>0.05206246301531792</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.02812889404594898</v>
+        <v>0.06987083703279495</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01979775913059711</v>
+        <v>0.1209941729903221</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.06688415259122849</v>
+        <v>0.1304734796285629</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.01723233237862587</v>
+        <v>0.1704907715320587</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.01287098508328199</v>
+        <v>0.1555847078561783</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.0168320257216692</v>
+        <v>0.0166848711669445</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.008485015481710434</v>
+        <v>0.09909988194704056</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.02061109244823456</v>
+        <v>0.1364023387432098</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.0678454264998436</v>
+        <v>0.2471497058868408</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.02621154114603996</v>
+        <v>0.1200108975172043</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.02008281648159027</v>
+        <v>0.04776932671666145</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.002513394458219409</v>
+        <v>0.02846800722181797</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.02017840184271336</v>
+        <v>0.008517814800143242</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.007532679475843906</v>
+        <v>0.02839231863617897</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.02520492300391197</v>
+        <v>0.1061835959553719</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.01175673492252827</v>
+        <v>0.03085255436599255</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.004549136385321617</v>
+        <v>0.059417724609375</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.03398407995700836</v>
+        <v>0.02950759045779705</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.01573731750249863</v>
+        <v>0.01855984516441822</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.02018899843096733</v>
+        <v>0.06358715891838074</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.003694717306643724</v>
+        <v>0.05743314325809479</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.009547235444188118</v>
+        <v>0.01984417997300625</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.01422717235982418</v>
+        <v>0.04218508303165436</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.002075456781312823</v>
+        <v>0.03629989922046661</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.01179154310375452</v>
+        <v>0.08364662528038025</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.0407247357070446</v>
+        <v>0.0825350284576416</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.05404458194971085</v>
+        <v>0.1091904863715172</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.005344482138752937</v>
+        <v>0.1768571138381958</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.003744068555533886</v>
+        <v>0.07910957932472229</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.03742179274559021</v>
+        <v>0.1181607246398926</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.01878031902015209</v>
+        <v>0.03710861131548882</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.001900121569633484</v>
+        <v>0.2088057994842529</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.006773190572857857</v>
+        <v>0.1189235299825668</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.00694127194583416</v>
+        <v>0.09684950113296509</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.007499187253415585</v>
+        <v>0.0477379709482193</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.02713833563029766</v>
+        <v>0.03301918506622314</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.02096076123416424</v>
+        <v>0.01173657923936844</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.02927112951874733</v>
+        <v>0.05722153186798096</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.001783945946954191</v>
+        <v>0.0499391220510006</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.004525688476860523</v>
+        <v>0.003288749372586608</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.01872164383530617</v>
+        <v>0.05671074986457825</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.003218716010451317</v>
+        <v>0.04946661740541458</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.009199893102049828</v>
+        <v>0.061724703758955</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.0129935909062624</v>
+        <v>0.08739794790744781</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.09620144218206406</v>
+        <v>0.05671723932027817</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.01805428601801395</v>
+        <v>0.2122152745723724</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.04345276951789856</v>
+        <v>0.05228706076741219</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.04394727572798729</v>
+        <v>0.06455668807029724</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.008470212109386921</v>
+        <v>0.0821615532040596</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.03157566487789154</v>
+        <v>0.04963509365916252</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.01081379316747189</v>
+        <v>0.2029105424880981</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.02822907827794552</v>
+        <v>0.0149715393781662</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.004779631271958351</v>
+        <v>0.07099797576665878</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.02242838405072689</v>
+        <v>0.02285410091280937</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.01926388964056969</v>
+        <v>0.07184527069330215</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01159104891121387</v>
+        <v>0.1438292115926743</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01152861956506968</v>
+        <v>0.09796523302793503</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.003234990639612079</v>
+        <v>0.2051306962966919</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.01033906545490026</v>
+        <v>0.1094910353422165</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.001245525549165905</v>
+        <v>7.807160727679729e-05</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.01328951492905617</v>
+        <v>0.08343160897493362</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.005165623035281897</v>
+        <v>0.03527233004570007</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01781869679689407</v>
+        <v>0.07124267518520355</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.01196662150323391</v>
+        <v>0.03311790898442268</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.02375212870538235</v>
+        <v>0.04248007014393806</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01637517474591732</v>
+        <v>0.1074664667248726</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.005139475222676992</v>
+        <v>0.02741815149784088</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.004908929113298655</v>
+        <v>0.005750864744186401</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.02039369009435177</v>
+        <v>0.1046091467142105</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.007403751369565725</v>
+        <v>0.03653988987207413</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.01639188081026077</v>
+        <v>0.04027354344725609</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.005791539791971445</v>
+        <v>0.03839071467518806</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.01165638025850058</v>
+        <v>0.005361107178032398</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.02584907785058022</v>
+        <v>0.01960787549614906</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.001220104866661131</v>
+        <v>0.02188050001859665</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.009981258772313595</v>
+        <v>0.01565339416265488</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.0179870929569006</v>
+        <v>0.03472474589943886</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.01379217207431793</v>
+        <v>0.02333784662187099</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.004771940875798464</v>
+        <v>0.06763366609811783</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.02146852761507034</v>
+        <v>0.1144504696130753</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.01083813887089491</v>
+        <v>0.005549084395170212</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.02908244170248508</v>
+        <v>0.02972135879099369</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.02162539027631283</v>
+        <v>0.1305120289325714</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.009593983180820942</v>
+        <v>0.005224802531301975</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.0192874800413847</v>
+        <v>0.01982493884861469</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.01812324859201908</v>
+        <v>0.104625478386879</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.009983177296817303</v>
+        <v>0.04284670203924179</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.00060926319565624</v>
+        <v>0.05185903981328011</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.006733211223036051</v>
+        <v>0.04826308414340019</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.0254362802952528</v>
+        <v>0.02680520340800285</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.01553015783429146</v>
+        <v>0.001653374172747135</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.02168773114681244</v>
+        <v>0.02571109309792519</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.004393397364765406</v>
+        <v>0.02421385049819946</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.008303079754114151</v>
+        <v>0.01816909573972225</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.0213442537933588</v>
+        <v>0.03157732635736465</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.005708687473088503</v>
+        <v>0.07612764835357666</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.01260432042181492</v>
+        <v>0.07179659605026245</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.02289289236068726</v>
+        <v>0.1431098431348801</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01121392566710711</v>
+        <v>0.04710379987955093</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.01420513074845076</v>
+        <v>0.0689358189702034</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.01582640409469604</v>
+        <v>0.1508956998586655</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.02023430913686752</v>
+        <v>0.08707040548324585</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.01138448715209961</v>
+        <v>0.08276426792144775</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.002915454562753439</v>
+        <v>0.05843707546591759</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.009559748694300652</v>
+        <v>0.1111486405134201</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.002640916267409921</v>
+        <v>0.2710641026496887</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.009429987519979477</v>
+        <v>0.1399058103561401</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.02265161648392677</v>
+        <v>0.2082339525222778</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.01594454981386662</v>
+        <v>0.3096722364425659</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.03036906942725182</v>
+        <v>0.2546826004981995</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.03440292179584503</v>
+        <v>0.04655822739005089</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01892963238060474</v>
+        <v>0.2100842148065567</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.03966683149337769</v>
+        <v>0.1010463684797287</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.03036275878548622</v>
+        <v>0.1520941555500031</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.009992369450628757</v>
+        <v>0.1333109736442566</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.02859909646213055</v>
+        <v>0.05032160505652428</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.02263999171555042</v>
+        <v>0.1080801710486412</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.00462054880335927</v>
+        <v>0.0707605704665184</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.02345587126910686</v>
+        <v>0.04465218260884285</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.009119094349443913</v>
+        <v>0.06826306879520416</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.01044301223009825</v>
+        <v>0.005814353004097939</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.04068347439169884</v>
+        <v>0.04043807461857796</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.02861273847520351</v>
+        <v>0.03187985345721245</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.0192599818110466</v>
+        <v>0.04175277054309845</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.005577217787504196</v>
+        <v>0.05389337241649628</v>
       </c>
       <c r="B13" t="n">
-        <v>0.08181694895029068</v>
+        <v>0.185519203543663</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0112439664080739</v>
+        <v>0.1952701807022095</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02774927578866482</v>
+        <v>0.2981773018836975</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01555256918072701</v>
+        <v>0.6737170219421387</v>
       </c>
       <c r="F13" t="n">
-        <v>0.008924899622797966</v>
+        <v>0.6017465591430664</v>
       </c>
       <c r="G13" t="n">
-        <v>0.005500447005033493</v>
+        <v>0.3297554552555084</v>
       </c>
       <c r="H13" t="n">
-        <v>0.002667081076651812</v>
+        <v>0.2405070960521698</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02973940782248974</v>
+        <v>0.1361515522003174</v>
       </c>
       <c r="J13" t="n">
-        <v>0.006564578041434288</v>
+        <v>0.1810020506381989</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06162454187870026</v>
+        <v>0.4761990010738373</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0003935341374017298</v>
+        <v>0.3728904724121094</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03025171346962452</v>
+        <v>0.03064160048961639</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02874569222331047</v>
+        <v>0.7993561625480652</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01478722132742405</v>
+        <v>0.7551203966140747</v>
       </c>
       <c r="P13" t="n">
-        <v>0.007391892373561859</v>
+        <v>0.3321599662303925</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.009984508156776428</v>
+        <v>0.2161372452974319</v>
       </c>
       <c r="R13" t="n">
-        <v>0.02296563982963562</v>
+        <v>0.2193748354911804</v>
       </c>
       <c r="S13" t="n">
-        <v>0.000629714981187135</v>
+        <v>0.0298592746257782</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01806139200925827</v>
+        <v>0.1135057806968689</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01222300715744495</v>
+        <v>8.367374539375305e-05</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0101562300696969</v>
+        <v>0.2630538046360016</v>
       </c>
       <c r="W13" t="n">
-        <v>0.00310497940517962</v>
+        <v>0.1689379662275314</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01336128637194633</v>
+        <v>0.1468353569507599</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.003184475935995579</v>
+        <v>0.02331526950001717</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.002065240172669291</v>
+        <v>0.04381395876407623</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.005586629267781973</v>
+        <v>0.0916081964969635</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.007040683180093765</v>
+        <v>0.1126716881990433</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.012672477401793</v>
+        <v>0.1031390205025673</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.001511023263446987</v>
+        <v>0.1675900965929031</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.002878102706745267</v>
+        <v>0.1155004054307938</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.002717307303100824</v>
+        <v>0.202879399061203</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.007587906904518604</v>
+        <v>0.2352645248174667</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.003580895951017737</v>
+        <v>0.1972766369581223</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.01166909281164408</v>
+        <v>0.3776834607124329</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.004049635492265224</v>
+        <v>0.02160757407546043</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.00681639090180397</v>
+        <v>0.1097727417945862</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.00700068287551403</v>
+        <v>0.2747164666652679</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.004760242067277431</v>
+        <v>0.003168553113937378</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0005591129884123802</v>
+        <v>0.113018810749054</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.009868954308331013</v>
+        <v>0.192562460899353</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.008202323690056801</v>
+        <v>0.08232489228248596</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.005432981066405773</v>
+        <v>0.1003870368003845</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.001061122864484787</v>
+        <v>0.1901759952306747</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.002713993657380342</v>
+        <v>0.05665198341012001</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.00717720203101635</v>
+        <v>0.3014386892318726</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.0612245686352253</v>
+        <v>1.202896118164062</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.001353890518657863</v>
+        <v>0.05848468095064163</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.002556977793574333</v>
+        <v>0.1479659527540207</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.002106440253555775</v>
+        <v>0.3259031772613525</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0006088865920901299</v>
+        <v>0.3131694793701172</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.006376376841217279</v>
+        <v>0.09231927990913391</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.001268741209059954</v>
+        <v>0.1446408927440643</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.006994714960455894</v>
+        <v>0.1319495886564255</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.002461488358676434</v>
+        <v>0.1535929441452026</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.02171889320015907</v>
+        <v>0.5166409015655518</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.01353149674832821</v>
+        <v>0.08632966876029968</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.004940791986882687</v>
+        <v>0.3723616302013397</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.02272762358188629</v>
+        <v>0.6266840100288391</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.01723606139421463</v>
+        <v>0.0856429859995842</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.002239266876131296</v>
+        <v>0.01833129674196243</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.01201801467686892</v>
+        <v>0.1302632838487625</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01018952764570713</v>
+        <v>0.1082834154367447</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.007259672973304987</v>
+        <v>0.05854436755180359</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.01932142861187458</v>
+        <v>0.3092694878578186</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.00745469331741333</v>
+        <v>0.04244176298379898</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.0004404140636324883</v>
+        <v>0.03436722978949547</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.0320940837264061</v>
+        <v>0.4657980501651764</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.01541776955127716</v>
+        <v>0.3766899704933167</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0002983546582981944</v>
+        <v>0.4529788792133331</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.006778035778552294</v>
+        <v>0.1310576647520065</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.001143224537372589</v>
+        <v>0.06186643615365028</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.004162495024502277</v>
+        <v>0.1776574999094009</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.03687386214733124</v>
+        <v>0.6531293988227844</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.007553076837211847</v>
+        <v>0.09496311098337173</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.006883584894239902</v>
+        <v>0.3661543726921082</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.003288321197032928</v>
+        <v>0.114222839474678</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.01656896993517876</v>
+        <v>0.1313687264919281</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.01015130430459976</v>
+        <v>0.03311386331915855</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.0009626783430576324</v>
+        <v>0.02422602660953999</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.009509571827948093</v>
+        <v>0.175955057144165</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0004868190153501928</v>
+        <v>0.05599280446767807</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.01571660675108433</v>
+        <v>0.1927782893180847</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.0008142953156493604</v>
+        <v>0.02774217166006565</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.006157900672405958</v>
+        <v>0.03098182193934917</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.001928249490447342</v>
+        <v>0.0804625004529953</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0002277829335071146</v>
+        <v>0.1382328271865845</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0002623059554025531</v>
+        <v>0.1584276556968689</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.002545910654589534</v>
+        <v>0.02723870426416397</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.008202461525797844</v>
+        <v>0.03612667322158813</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.02128502726554871</v>
+        <v>0.1343175172805786</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.02638017758727074</v>
+        <v>0.7078018188476562</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0006120869074948132</v>
+        <v>0.140480563044548</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.00505746528506279</v>
+        <v>0.1989784836769104</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01283807959407568</v>
+        <v>0.06532818824052811</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.005179241765290499</v>
+        <v>0.2629852592945099</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.006036272272467613</v>
+        <v>0.2662023305892944</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01876058056950569</v>
+        <v>0.07553060352802277</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.0007480415515601635</v>
+        <v>0.02195831015706062</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0006716311909258366</v>
+        <v>0.01292086765170097</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.01276132371276617</v>
+        <v>0.1433753818273544</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.004110593348741531</v>
+        <v>0.02631379291415215</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.007710284553468227</v>
+        <v>0.03687817230820656</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.0005507836467586458</v>
+        <v>0.09552638977766037</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.00246357312425971</v>
+        <v>0.1365492194890976</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.000553128425963223</v>
+        <v>0.05709947645664215</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.0004371636314317584</v>
+        <v>0.04681238159537315</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.006601123139262199</v>
+        <v>0.01573861762881279</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.01504436228424311</v>
+        <v>0.2546145617961884</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.04893117025494576</v>
+        <v>0.296868771314621</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.007764552719891071</v>
+        <v>0.03162557259202003</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.02690008655190468</v>
+        <v>0.3150376677513123</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.003283495781943202</v>
+        <v>0.1210169494152069</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.001130824559368193</v>
+        <v>0.1597382724285126</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.02275311574339867</v>
+        <v>0.2538993656635284</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.007513593882322311</v>
+        <v>0.4203965663909912</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.00869280006736517</v>
+        <v>0.1211379244923592</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.008954067714512348</v>
+        <v>0.008225694298744202</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.01307326927781105</v>
+        <v>0.02128306403756142</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.007744127418845892</v>
+        <v>0.1646009981632233</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.009497127495706081</v>
+        <v>0.2586857676506042</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.003453061450272799</v>
+        <v>0.2458341866731644</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0003907356294803321</v>
+        <v>0.02900685369968414</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.01342370361089706</v>
+        <v>0.0460711233317852</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.001012612250633538</v>
+        <v>0.1541027575731277</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0005890540778636932</v>
+        <v>0.07013501226902008</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.005858222953975201</v>
+        <v>0.03776542097330093</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.006299820728600025</v>
+        <v>0.3247818946838379</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.006810321938246489</v>
+        <v>0.1399787068367004</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.008689533919095993</v>
+        <v>0.04982905089855194</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.008980863727629185</v>
+        <v>0.2780800461769104</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.005187788046896458</v>
+        <v>0.2623618543148041</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.005958992056548595</v>
+        <v>0.1296665370464325</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.005807351786643267</v>
+        <v>0.04042774438858032</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.001264015212655067</v>
+        <v>0.06068208441138268</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.002550193341448903</v>
+        <v>0.03029918298125267</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.001215407974086702</v>
+        <v>0.1751070767641068</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.00156169175170362</v>
+        <v>0.07570625841617584</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.005013321526348591</v>
+        <v>0.09232465922832489</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.003439276479184628</v>
+        <v>0.000123920850455761</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.001821031095460057</v>
+        <v>0.2414435893297195</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.003527778200805187</v>
+        <v>0.05487807467579842</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.002081247046589851</v>
+        <v>0.03242063522338867</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.009068487212061882</v>
+        <v>0.04612269252538681</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.007313637528568506</v>
+        <v>0.2081719934940338</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.005893096327781677</v>
+        <v>0.1607763469219208</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.006061414256691933</v>
+        <v>0.02161466144025326</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.00801367312669754</v>
+        <v>0.1354101002216339</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.005950230173766613</v>
+        <v>0.08139629662036896</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.01501781307160854</v>
+        <v>0.132314071059227</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.004631198011338711</v>
+        <v>0.07864619046449661</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.007759266532957554</v>
+        <v>0.2002111673355103</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.004215966910123825</v>
+        <v>0.1207424998283386</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0001922965748235583</v>
+        <v>0.02402833104133606</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.01377889793366194</v>
+        <v>0.2227818071842194</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.002160920994356275</v>
+        <v>0.001098076347261667</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.006617360282689333</v>
+        <v>0.03278781101107597</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0008429228328168392</v>
+        <v>0.08095364272594452</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.004469577688723803</v>
+        <v>0.1343317478895187</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.001931151957251132</v>
+        <v>0.1544724851846695</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.003167775459587574</v>
+        <v>0.02030820026993752</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.006063043605536222</v>
+        <v>0.05148694664239883</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.004829824436455965</v>
+        <v>0.119845412671566</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.005960780661553144</v>
+        <v>0.1624675095081329</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.001863262965343893</v>
+        <v>0.02265202254056931</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.006913785357028246</v>
+        <v>0.3378913402557373</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.00540013425052166</v>
+        <v>0.2274728715419769</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.003205910790711641</v>
+        <v>0.1251253634691238</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.004379042889922857</v>
+        <v>0.07500606030225754</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.00561832170933485</v>
+        <v>0.2981487512588501</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.01132174395024776</v>
+        <v>0.0306413322687149</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.003424943191930652</v>
+        <v>0.01092136185616255</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.008656037040054798</v>
+        <v>0.06303887069225311</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01120005268603563</v>
+        <v>0.02871847152709961</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.006004481576383114</v>
+        <v>0.08774931728839874</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.01260336302220821</v>
+        <v>0.459890604019165</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.009432514198124409</v>
+        <v>0.149188831448555</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.001744563924148679</v>
+        <v>0.01044047623872757</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.004155617207288742</v>
+        <v>0.328786164522171</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.004282622598111629</v>
+        <v>0.1617700755596161</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.003095870837569237</v>
+        <v>0.1139845848083496</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01771042123436928</v>
+        <v>0.06056971102952957</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.01003994420170784</v>
+        <v>0.06479628384113312</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.01269154902547598</v>
+        <v>0.1270929276943207</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.01587923616170883</v>
+        <v>0.04101794213056564</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.01837657205760479</v>
+        <v>0.2070814520120621</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.01211925037205219</v>
+        <v>0.06060050427913666</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.003012942150235176</v>
+        <v>0.250916451215744</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.003402496920898557</v>
+        <v>0.1016482710838318</v>
       </c>
     </row>
     <row r="14">
@@ -8396,1140 +8396,1140 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.02057583630084991</v>
+        <v>0.208573654294014</v>
       </c>
       <c r="B15" t="n">
-        <v>0.07483111321926117</v>
+        <v>0.3172373175621033</v>
       </c>
       <c r="C15" t="n">
-        <v>0.04906534403562546</v>
+        <v>0.1885339617729187</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01722148805856705</v>
+        <v>0.1763462722301483</v>
       </c>
       <c r="E15" t="n">
-        <v>0.08054881542921066</v>
+        <v>0.2233962565660477</v>
       </c>
       <c r="F15" t="n">
-        <v>0.006956384982913733</v>
+        <v>0.01358112320303917</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04447163268923759</v>
+        <v>0.1190228387713432</v>
       </c>
       <c r="H15" t="n">
-        <v>0.01133394800126553</v>
+        <v>0.05484369397163391</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02648514322936535</v>
+        <v>0.06924132257699966</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01259789243340492</v>
+        <v>0.1079049408435822</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05307179689407349</v>
+        <v>0.3736228346824646</v>
       </c>
       <c r="L15" t="n">
-        <v>0.03256750106811523</v>
+        <v>0.1365889757871628</v>
       </c>
       <c r="M15" t="n">
-        <v>0.03793755918741226</v>
+        <v>0.1703865528106689</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1140828654170036</v>
+        <v>0.2573006749153137</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02053695730865002</v>
+        <v>0.01405664533376694</v>
       </c>
       <c r="P15" t="n">
-        <v>0.03698839247226715</v>
+        <v>0.1481099724769592</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.00868544727563858</v>
+        <v>0.002519675297662616</v>
       </c>
       <c r="R15" t="n">
-        <v>0.01171412132680416</v>
+        <v>0.1136164963245392</v>
       </c>
       <c r="S15" t="n">
-        <v>0.00317345978692174</v>
+        <v>0.01628803834319115</v>
       </c>
       <c r="T15" t="n">
-        <v>0.02187497168779373</v>
+        <v>0.1288940608501434</v>
       </c>
       <c r="U15" t="n">
-        <v>0.001426278962753713</v>
+        <v>0.114333763718605</v>
       </c>
       <c r="V15" t="n">
-        <v>0.007074854802340269</v>
+        <v>0.06630455702543259</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01103164441883564</v>
+        <v>0.05573893710970879</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01635158434510231</v>
+        <v>0.06507977098226547</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.004036804661154747</v>
+        <v>0.01503988169133663</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.004362444393336773</v>
+        <v>0.02314917556941509</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.001436148420907557</v>
+        <v>0.03872335329651833</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.008066023699939251</v>
+        <v>0.1238154768943787</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.02454878017306328</v>
+        <v>0.05569728091359138</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.009242060594260693</v>
+        <v>0.1425889581441879</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0006583421491086483</v>
+        <v>0.1403150409460068</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.00960334949195385</v>
+        <v>0.05120872333645821</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.005722085945308208</v>
+        <v>0.04238179326057434</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.006389723159372807</v>
+        <v>0.01010015606880188</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.01486492902040482</v>
+        <v>0.2017378807067871</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.01306821219623089</v>
+        <v>0.1256821304559708</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.004867134150117636</v>
+        <v>0.01439259201288223</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.03691645339131355</v>
+        <v>0.2128859460353851</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.002818814478814602</v>
+        <v>0.03841333091259003</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.002838947810232639</v>
+        <v>0.04727935418486595</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.01108430046588182</v>
+        <v>0.2198677062988281</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.02155855111777782</v>
+        <v>0.032535620033741</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.01011637877672911</v>
+        <v>0.03200989589095116</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.01762829348444939</v>
+        <v>0.09746389091014862</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.024378577247262</v>
+        <v>0.04103263467550278</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.03590576723217964</v>
+        <v>0.01642303727567196</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.08778438717126846</v>
+        <v>0.3130699992179871</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.03726780787110329</v>
+        <v>0.05986158177256584</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.02334977686405182</v>
+        <v>0.1061585992574692</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.01487364806234837</v>
+        <v>0.008186381310224533</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.01033271756023169</v>
+        <v>0.03852006420493126</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.01862562447786331</v>
+        <v>0.03467405587434769</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.01421504933387041</v>
+        <v>0.08606088906526566</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.01691875793039799</v>
+        <v>0.01628059148788452</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.01386817172169685</v>
+        <v>0.1642127633094788</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.007554469630122185</v>
+        <v>0.2054208964109421</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.01935680210590363</v>
+        <v>0.2295039892196655</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.02994317933917046</v>
+        <v>0.0752071887254715</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.08335790783166885</v>
+        <v>0.3721106052398682</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.01776295714080334</v>
+        <v>0.0330011323094368</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.01877301931381226</v>
+        <v>0.04306293278932571</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.01225454546511173</v>
+        <v>0.06702148914337158</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.01564279943704605</v>
+        <v>0.04327499866485596</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.02889508567750454</v>
+        <v>0.0538603737950325</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.02272121235728264</v>
+        <v>0.03227399289608002</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.01437527593225241</v>
+        <v>0.02291166223585606</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.01574861258268356</v>
+        <v>0.1224182397127151</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.06987655907869339</v>
+        <v>0.0426391139626503</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.009744852781295776</v>
+        <v>0.01009784266352654</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.01798508316278458</v>
+        <v>0.07727707177400589</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.03071337565779686</v>
+        <v>0.03113803267478943</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.01180544495582581</v>
+        <v>0.07192901521921158</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.02315126359462738</v>
+        <v>0.04856633767485619</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.03904903680086136</v>
+        <v>0.3999703526496887</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.04626278206706047</v>
+        <v>0.08445804566144943</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.001457519829273224</v>
+        <v>0.01880844682455063</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.006299713626503944</v>
+        <v>0.003765501081943512</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.004780526272952557</v>
+        <v>0.030814403668046</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.02566493488848209</v>
+        <v>0.0799933448433876</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.004976019263267517</v>
+        <v>0.01598303392529488</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.00621710903942585</v>
+        <v>0.03050775453448296</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.005549275316298008</v>
+        <v>0.02210034243762493</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.01665555499494076</v>
+        <v>0.1545633673667908</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.00274688983336091</v>
+        <v>0.05415721610188484</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.01360672991722822</v>
+        <v>0.08575692772865295</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.01522816997021437</v>
+        <v>0.02585160359740257</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.001405325368978083</v>
+        <v>0.01213132217526436</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.0004023009678348899</v>
+        <v>0.009314173832535744</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.001235356670804322</v>
+        <v>0.0002275388687849045</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.006800883449614048</v>
+        <v>0.01557097863405943</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.03501879423856735</v>
+        <v>0.1128601878881454</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.01121234335005283</v>
+        <v>0.1550381928682327</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.01463074423372746</v>
+        <v>0.03168440237641335</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.008124202489852905</v>
+        <v>0.1311443895101547</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.001289255917072296</v>
+        <v>0.2108310014009476</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.01241162698715925</v>
+        <v>0.01274760346859694</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.003107709810137749</v>
+        <v>0.03159291669726372</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.00127884466201067</v>
+        <v>0.08885671198368073</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.008939040824770927</v>
+        <v>0.07880939543247223</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.006797000300139189</v>
+        <v>0.0003962237387895584</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.01034891325980425</v>
+        <v>0.1386588662862778</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.001718280371278524</v>
+        <v>0.05582920834422112</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.009373711422085762</v>
+        <v>0.05684909969568253</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.01425518002361059</v>
+        <v>0.02967816218733788</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.0002338969643460587</v>
+        <v>0.01762011274695396</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.001326714176684618</v>
+        <v>0.003143352456390858</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.0007312120869755745</v>
+        <v>0.01616920903325081</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.01005438528954983</v>
+        <v>0.03358342498540878</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.008131092414259911</v>
+        <v>0.08603423833847046</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.04333688318729401</v>
+        <v>0.1046762317419052</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.003267666324973106</v>
+        <v>0.005283284932374954</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.01692524366080761</v>
+        <v>0.02535082027316093</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.01770849339663982</v>
+        <v>0.07121902704238892</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.009533029049634933</v>
+        <v>0.1376437693834305</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.03285215795040131</v>
+        <v>0.009468735195696354</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.01911308243870735</v>
+        <v>0.05972667410969734</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.0144334901124239</v>
+        <v>0.08793509006500244</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.01907974109053612</v>
+        <v>0.02975823543965816</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.01580966077744961</v>
+        <v>0.0867876261472702</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.008707751519978046</v>
+        <v>0.01178391650319099</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.01191053353250027</v>
+        <v>0.01344046369194984</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.007787025533616543</v>
+        <v>0.06378767639398575</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.01631184108555317</v>
+        <v>0.1318162977695465</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.02252066507935524</v>
+        <v>0.0140572777017951</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.02287577465176582</v>
+        <v>0.03567849844694138</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.004789398517459631</v>
+        <v>0.003892915323376656</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.02341415360569954</v>
+        <v>0.08840138465166092</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.007283469662070274</v>
+        <v>0.162303239107132</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.004801771137863398</v>
+        <v>0.1078297048807144</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.01867637597024441</v>
+        <v>0.01551616098731756</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01162310037761927</v>
+        <v>0.04501234740018845</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.02449572272598743</v>
+        <v>0.05536608770489693</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.005285193212330341</v>
+        <v>0.04143598303198814</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.002437445567920804</v>
+        <v>0.01545990351587534</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.003006317187100649</v>
+        <v>0.09460791200399399</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.000155535526573658</v>
+        <v>0.04059698432683945</v>
       </c>
       <c r="EG15" t="n">
-        <v>8.134241215884686e-05</v>
+        <v>0.06202013790607452</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.004307840019464493</v>
+        <v>0.03090254962444305</v>
       </c>
       <c r="EI15" t="n">
-        <v>0.01603903621435165</v>
+        <v>0.09107731282711029</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.01840828731656075</v>
+        <v>0.01076906733214855</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.0009549966780468822</v>
+        <v>0.01645872741937637</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.01874890737235546</v>
+        <v>0.007240495178848505</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.008487431332468987</v>
+        <v>0.02047220803797245</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.01313724275678396</v>
+        <v>0.002481120405718684</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.008100053295493126</v>
+        <v>0.01930510252714157</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.001004362478852272</v>
+        <v>0.1310428082942963</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.01943324878811836</v>
+        <v>0.03814133256673813</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.005500687751919031</v>
+        <v>0.09438575804233551</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.01042971666902304</v>
+        <v>0.02425180934369564</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.006556629668921232</v>
+        <v>0.08609741926193237</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.02445177361369133</v>
+        <v>0.01268716063350439</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.01576049998402596</v>
+        <v>0.02655536867678165</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.02433540858328342</v>
+        <v>0.04862044751644135</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.005366778932511806</v>
+        <v>0.02486972697079182</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.01103915367275476</v>
+        <v>0.1592579185962677</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.001555830240249634</v>
+        <v>0.04224755242466927</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.0123233525082469</v>
+        <v>0.06635064631700516</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.01921996846795082</v>
+        <v>0.03264060616493225</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.001667438074946404</v>
+        <v>0.02227400057017803</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.003719652537256479</v>
+        <v>0.01185840368270874</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.002603244502097368</v>
+        <v>0.01757766865193844</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.0022417395375669</v>
+        <v>0.03399462252855301</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.02794861234724522</v>
+        <v>0.01918778568506241</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.01844304427504539</v>
+        <v>0.02348167076706886</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.01132637169212103</v>
+        <v>0.05966011807322502</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.001578046474605799</v>
+        <v>0.003474026918411255</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.01332500111311674</v>
+        <v>0.03975235298275948</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.002739546354860067</v>
+        <v>0.07705966383218765</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.01649260893464088</v>
+        <v>0.01822825893759727</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.0194072350859642</v>
+        <v>0.0957832932472229</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.01610025390982628</v>
+        <v>0.0005406662821769714</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.01316785998642445</v>
+        <v>0.1311964690685272</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.01469191629439592</v>
+        <v>0.02843369916081429</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.02303907088935375</v>
+        <v>0.01674207299947739</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.03438026830554008</v>
+        <v>0.00746418721973896</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.02160557731986046</v>
+        <v>0.1818085461854935</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.007109254598617554</v>
+        <v>0.09493075311183929</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.0008793817833065987</v>
+        <v>0.1065271869301796</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.02773472294211388</v>
+        <v>0.04589527472853661</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.01125966012477875</v>
+        <v>0.1325611472129822</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.007975019514560699</v>
+        <v>0.003126546740531921</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.01593546196818352</v>
+        <v>0.1122446581721306</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.008739657700061798</v>
+        <v>0.01323871500790119</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.02642921544611454</v>
+        <v>0.0004523377865552902</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.004086407832801342</v>
+        <v>0.05215658992528915</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.03158072754740715</v>
+        <v>0.03368472307920456</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.02497965283691883</v>
+        <v>0.005891518667340279</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.006407864391803741</v>
+        <v>0.0258894432336092</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.004514980129897594</v>
+        <v>0.03430851176381111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.428835093975067e-05</v>
+        <v>3.697387728607282e-05</v>
       </c>
       <c r="B16" t="n">
-        <v>9.338073141407222e-05</v>
+        <v>4.10378779633902e-05</v>
       </c>
       <c r="C16" t="n">
-        <v>4.142770194448531e-05</v>
+        <v>1.34307501866715e-05</v>
       </c>
       <c r="D16" t="n">
-        <v>2.67312989308266e-05</v>
+        <v>2.252990816486999e-05</v>
       </c>
       <c r="E16" t="n">
-        <v>3.405228926567361e-05</v>
+        <v>7.804691995261237e-05</v>
       </c>
       <c r="F16" t="n">
-        <v>9.266459528589621e-06</v>
+        <v>1.202747171191731e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>4.200219336780719e-07</v>
+        <v>2.973143637063913e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>2.515717824280728e-05</v>
+        <v>3.132872370770201e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>3.966871190641541e-06</v>
+        <v>9.439229870622512e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>3.473569449852221e-07</v>
+        <v>4.418234311742708e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>6.621307693421841e-05</v>
+        <v>9.791197226149961e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>1.699189488135744e-05</v>
+        <v>2.689934808586258e-05</v>
       </c>
       <c r="M16" t="n">
-        <v>2.555420724092983e-05</v>
+        <v>4.438713222043589e-05</v>
       </c>
       <c r="N16" t="n">
-        <v>5.147325282450765e-05</v>
+        <v>8.723707287572324e-05</v>
       </c>
       <c r="O16" t="n">
-        <v>8.505834557581693e-06</v>
+        <v>1.23791214718949e-05</v>
       </c>
       <c r="P16" t="n">
-        <v>2.399729964963626e-06</v>
+        <v>8.879511369741522e-06</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.058922165015247e-06</v>
+        <v>3.050226223422214e-05</v>
       </c>
       <c r="R16" t="n">
-        <v>1.243484916813031e-06</v>
+        <v>2.614804907352664e-05</v>
       </c>
       <c r="S16" t="n">
-        <v>2.427381787128979e-06</v>
+        <v>9.26080065255519e-06</v>
       </c>
       <c r="T16" t="n">
-        <v>2.016581674979534e-05</v>
+        <v>1.349974172626389e-05</v>
       </c>
       <c r="U16" t="n">
-        <v>7.499852472392377e-06</v>
+        <v>4.060791252413765e-05</v>
       </c>
       <c r="V16" t="n">
-        <v>5.602098099188879e-06</v>
+        <v>3.935314089176245e-05</v>
       </c>
       <c r="W16" t="n">
-        <v>2.990789198520361e-07</v>
+        <v>3.002000448759645e-05</v>
       </c>
       <c r="X16" t="n">
-        <v>3.123104033875279e-05</v>
+        <v>6.709297849738505e-06</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.726216841139831e-06</v>
+        <v>1.063759646058315e-05</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.954111939994618e-05</v>
+        <v>3.214110620319843e-06</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.481538442429155e-06</v>
+        <v>2.024388777499553e-06</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.09019129013177e-06</v>
+        <v>1.963381009773002e-06</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.332952135475352e-05</v>
+        <v>1.970686207641847e-05</v>
       </c>
       <c r="AD16" t="n">
-        <v>9.496336133452132e-06</v>
+        <v>2.13538278330816e-05</v>
       </c>
       <c r="AE16" t="n">
-        <v>4.947361958329566e-06</v>
+        <v>3.4838953979488e-06</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.649263685976621e-05</v>
+        <v>4.308525967644528e-05</v>
       </c>
       <c r="AG16" t="n">
-        <v>5.094738298794255e-06</v>
+        <v>1.341575080004986e-05</v>
       </c>
       <c r="AH16" t="n">
-        <v>5.553578375838697e-06</v>
+        <v>2.225822299806168e-06</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.158746833127225e-06</v>
+        <v>3.64442021236755e-05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.4290852707054e-07</v>
+        <v>9.360872354591265e-06</v>
       </c>
       <c r="AK16" t="n">
-        <v>7.700558853684925e-06</v>
+        <v>7.521121460740687e-06</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.822885835485067e-05</v>
+        <v>1.627865458431188e-05</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.103640326822642e-06</v>
+        <v>1.240832534676883e-05</v>
       </c>
       <c r="AN16" t="n">
-        <v>9.52256414166186e-07</v>
+        <v>1.066216555045685e-05</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.122400863096118e-05</v>
+        <v>3.660906804725528e-05</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.015481029753573e-05</v>
+        <v>1.486102610215312e-05</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.268935638014227e-06</v>
+        <v>8.513469765603077e-06</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.268274773901794e-06</v>
+        <v>3.452661258052103e-05</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.438257186237024e-05</v>
+        <v>1.56104433699511e-05</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.549760781927034e-05</v>
+        <v>2.413219044683501e-05</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0001001762939267792</v>
+        <v>0.0001119904482038692</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.083834806398954e-05</v>
+        <v>2.850657983799465e-05</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.830106601933949e-07</v>
+        <v>4.10183338317438e-06</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.061063267115969e-05</v>
+        <v>1.351299579255283e-05</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.505078777583549e-06</v>
+        <v>1.221781644744624e-06</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.755078746005893e-06</v>
+        <v>4.209300641377922e-06</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.073354153253604e-05</v>
+        <v>8.947397873271257e-06</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.356637196498923e-05</v>
+        <v>9.829383998294361e-06</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.447183977797977e-07</v>
+        <v>5.343316661310382e-05</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.709029558900511e-06</v>
+        <v>4.461138087208383e-05</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.951934973476455e-05</v>
+        <v>2.097826290992089e-05</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.479830285068601e-06</v>
+        <v>2.917085294029675e-05</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.752463766839355e-05</v>
+        <v>5.077641617390327e-05</v>
       </c>
       <c r="BH16" t="n">
-        <v>1.657468237681314e-05</v>
+        <v>1.765273736964446e-06</v>
       </c>
       <c r="BI16" t="n">
-        <v>4.647508831112646e-06</v>
+        <v>4.850817276746966e-06</v>
       </c>
       <c r="BJ16" t="n">
-        <v>6.351865522447042e-06</v>
+        <v>2.436477370793e-05</v>
       </c>
       <c r="BK16" t="n">
-        <v>8.740386874706019e-06</v>
+        <v>6.91422974341549e-06</v>
       </c>
       <c r="BL16" t="n">
-        <v>2.68265630438691e-05</v>
+        <v>8.964148037193809e-06</v>
       </c>
       <c r="BM16" t="n">
-        <v>2.562477129686158e-05</v>
+        <v>8.471930050291121e-05</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.207731111207977e-05</v>
+        <v>2.529129596950952e-05</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.542829340905882e-05</v>
+        <v>9.205375135934446e-06</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.164353958913125e-05</v>
+        <v>6.334135105134919e-05</v>
       </c>
       <c r="BQ16" t="n">
-        <v>9.951450010703411e-06</v>
+        <v>3.262323298258707e-05</v>
       </c>
       <c r="BR16" t="n">
-        <v>9.75253260548925e-06</v>
+        <v>5.01624344906304e-05</v>
       </c>
       <c r="BS16" t="n">
-        <v>2.005417263717391e-05</v>
+        <v>5.117595264891861e-06</v>
       </c>
       <c r="BT16" t="n">
-        <v>4.405737854540348e-06</v>
+        <v>6.628279152209871e-06</v>
       </c>
       <c r="BU16" t="n">
-        <v>1.375638385070488e-05</v>
+        <v>3.066341014346108e-05</v>
       </c>
       <c r="BV16" t="n">
-        <v>4.945105320075527e-05</v>
+        <v>6.733955524396151e-05</v>
       </c>
       <c r="BW16" t="n">
-        <v>3.078885492868721e-05</v>
+        <v>4.125776104046963e-05</v>
       </c>
       <c r="BX16" t="n">
-        <v>5.550747118832078e-06</v>
+        <v>1.85911740118172e-05</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.04853386094328e-05</v>
+        <v>2.770959872577805e-05</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.617120662762318e-05</v>
+        <v>1.132690340455156e-05</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.596556649019476e-05</v>
+        <v>2.56871098827105e-05</v>
       </c>
       <c r="CB16" t="n">
-        <v>8.423590998063446e-07</v>
+        <v>1.885919118649326e-07</v>
       </c>
       <c r="CC16" t="n">
-        <v>1.594760578882415e-05</v>
+        <v>6.710753950756043e-06</v>
       </c>
       <c r="CD16" t="n">
-        <v>6.900510470586596e-06</v>
+        <v>4.554463885142468e-06</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.59438895934727e-05</v>
+        <v>1.793540104699787e-05</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.008353249038919e-06</v>
+        <v>9.096082067117095e-06</v>
       </c>
       <c r="CG16" t="n">
-        <v>1.235542185895611e-05</v>
+        <v>2.455356707287137e-06</v>
       </c>
       <c r="CH16" t="n">
-        <v>2.11903795843682e-07</v>
+        <v>2.24989798880415e-05</v>
       </c>
       <c r="CI16" t="n">
-        <v>6.670194125035778e-06</v>
+        <v>6.880467935843626e-06</v>
       </c>
       <c r="CJ16" t="n">
-        <v>5.398431767389411e-06</v>
+        <v>4.078052370459773e-06</v>
       </c>
       <c r="CK16" t="n">
-        <v>4.778838956553955e-06</v>
+        <v>1.100256440622616e-06</v>
       </c>
       <c r="CL16" t="n">
-        <v>8.556488637623261e-07</v>
+        <v>7.026312687230529e-06</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.686978223209735e-05</v>
+        <v>3.492034738883376e-05</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.470951949362643e-05</v>
+        <v>6.368032336467877e-05</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.108369360736106e-05</v>
+        <v>2.192538204326411e-06</v>
       </c>
       <c r="CP16" t="n">
-        <v>3.374269908817951e-06</v>
+        <v>4.833226194023155e-05</v>
       </c>
       <c r="CQ16" t="n">
-        <v>1.570577660459094e-05</v>
+        <v>4.642415660782717e-06</v>
       </c>
       <c r="CR16" t="n">
-        <v>2.460757286826265e-06</v>
+        <v>3.200075298082083e-07</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.933611540356651e-07</v>
+        <v>1.340723792964127e-05</v>
       </c>
       <c r="CT16" t="n">
-        <v>1.292679712605604e-06</v>
+        <v>2.006386239372659e-07</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.481597337260609e-05</v>
+        <v>2.983015292556956e-07</v>
       </c>
       <c r="CV16" t="n">
-        <v>7.837722478143405e-06</v>
+        <v>2.643457719386788e-06</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.146716112998547e-05</v>
+        <v>2.013714583881665e-05</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.583936068527692e-06</v>
+        <v>8.182089004549198e-06</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.274879468837753e-05</v>
+        <v>1.614953544049058e-05</v>
       </c>
       <c r="CZ16" t="n">
-        <v>4.09421346603267e-07</v>
+        <v>1.078208060789621e-05</v>
       </c>
       <c r="DA16" t="n">
-        <v>8.329174306709319e-06</v>
+        <v>7.335626833082642e-06</v>
       </c>
       <c r="DB16" t="n">
-        <v>6.262046554184053e-06</v>
+        <v>8.155643627105746e-08</v>
       </c>
       <c r="DC16" t="n">
-        <v>3.958361503464403e-06</v>
+        <v>6.877947953398689e-07</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.84835948352702e-06</v>
+        <v>3.464271230768645e-06</v>
       </c>
       <c r="DE16" t="n">
-        <v>2.16142761928495e-05</v>
+        <v>2.009227318922058e-05</v>
       </c>
       <c r="DF16" t="n">
-        <v>3.122362977592275e-05</v>
+        <v>4.743147292174399e-05</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.428919858881272e-06</v>
+        <v>1.892093132482842e-05</v>
       </c>
       <c r="DH16" t="n">
-        <v>3.392662256374024e-05</v>
+        <v>2.428104562568478e-05</v>
       </c>
       <c r="DI16" t="n">
-        <v>2.352840601815842e-05</v>
+        <v>2.828326796588954e-05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.005581907520536e-05</v>
+        <v>1.316810084972531e-06</v>
       </c>
       <c r="DK16" t="n">
-        <v>1.470520874136128e-05</v>
+        <v>8.536151653970592e-06</v>
       </c>
       <c r="DL16" t="n">
-        <v>6.249644229683327e-06</v>
+        <v>6.725138064211933e-06</v>
       </c>
       <c r="DM16" t="n">
-        <v>1.603764940227848e-05</v>
+        <v>8.061216249188874e-06</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.435781086911447e-05</v>
+        <v>1.129474640038097e-05</v>
       </c>
       <c r="DO16" t="n">
-        <v>1.061913394551084e-06</v>
+        <v>1.786231950973161e-05</v>
       </c>
       <c r="DP16" t="n">
-        <v>6.809777460148325e-06</v>
+        <v>3.530336130097567e-07</v>
       </c>
       <c r="DQ16" t="n">
-        <v>8.305210030812304e-06</v>
+        <v>1.766356945154257e-05</v>
       </c>
       <c r="DR16" t="n">
-        <v>1.680347281762806e-06</v>
+        <v>1.805967622203752e-05</v>
       </c>
       <c r="DS16" t="n">
-        <v>3.708302074301173e-06</v>
+        <v>1.253428672498558e-05</v>
       </c>
       <c r="DT16" t="n">
-        <v>2.743097866186872e-06</v>
+        <v>4.89606009068666e-06</v>
       </c>
       <c r="DU16" t="n">
-        <v>1.177943613583921e-05</v>
+        <v>1.544349652249366e-05</v>
       </c>
       <c r="DV16" t="n">
-        <v>1.06503939605318e-05</v>
+        <v>5.410449830378639e-06</v>
       </c>
       <c r="DW16" t="n">
-        <v>1.386850181006594e-05</v>
+        <v>3.714553167810664e-05</v>
       </c>
       <c r="DX16" t="n">
-        <v>1.963678414540482e-06</v>
+        <v>5.326839891495183e-05</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.404848136298824e-06</v>
+        <v>1.276083094126079e-05</v>
       </c>
       <c r="DZ16" t="n">
-        <v>1.05880126284319e-05</v>
+        <v>9.132483683060855e-06</v>
       </c>
       <c r="EA16" t="n">
-        <v>2.002874316531233e-05</v>
+        <v>2.715789742069319e-05</v>
       </c>
       <c r="EB16" t="n">
-        <v>9.264423169952352e-06</v>
+        <v>1.930012876982801e-05</v>
       </c>
       <c r="EC16" t="n">
-        <v>8.422008249908686e-06</v>
+        <v>3.483617547317408e-06</v>
       </c>
       <c r="ED16" t="n">
-        <v>7.522634405177087e-06</v>
+        <v>1.275283830182161e-05</v>
       </c>
       <c r="EE16" t="n">
-        <v>6.656715868302854e-06</v>
+        <v>1.402124780724989e-07</v>
       </c>
       <c r="EF16" t="n">
-        <v>1.576092245159089e-06</v>
+        <v>2.266333467559889e-05</v>
       </c>
       <c r="EG16" t="n">
-        <v>6.083713287807768e-06</v>
+        <v>1.354844334855443e-05</v>
       </c>
       <c r="EH16" t="n">
-        <v>1.725515517136955e-06</v>
+        <v>7.549688234576024e-06</v>
       </c>
       <c r="EI16" t="n">
-        <v>1.702673398540355e-05</v>
+        <v>1.578228693688288e-05</v>
       </c>
       <c r="EJ16" t="n">
-        <v>8.247155165008735e-06</v>
+        <v>2.446277449053014e-06</v>
       </c>
       <c r="EK16" t="n">
-        <v>8.828307727526408e-06</v>
+        <v>1.173992859548889e-05</v>
       </c>
       <c r="EL16" t="n">
-        <v>8.815259207040071e-06</v>
+        <v>2.971059984702151e-07</v>
       </c>
       <c r="EM16" t="n">
-        <v>3.067561920033768e-06</v>
+        <v>5.83114342589397e-06</v>
       </c>
       <c r="EN16" t="n">
-        <v>3.71537726095994e-06</v>
+        <v>1.146096292359289e-05</v>
       </c>
       <c r="EO16" t="n">
-        <v>5.267805136099923e-06</v>
+        <v>4.093079951417167e-06</v>
       </c>
       <c r="EP16" t="n">
-        <v>7.737598025414627e-06</v>
+        <v>1.558646886223869e-06</v>
       </c>
       <c r="EQ16" t="n">
-        <v>8.783470548223704e-06</v>
+        <v>9.037736163008958e-06</v>
       </c>
       <c r="ER16" t="n">
-        <v>2.621421572257532e-06</v>
+        <v>2.192571628256701e-06</v>
       </c>
       <c r="ES16" t="n">
-        <v>3.912513193427003e-07</v>
+        <v>1.682928268564865e-05</v>
       </c>
       <c r="ET16" t="n">
-        <v>1.877669637906365e-05</v>
+        <v>1.045070348482113e-05</v>
       </c>
       <c r="EU16" t="n">
-        <v>1.781795799615793e-05</v>
+        <v>7.503663709940156e-06</v>
       </c>
       <c r="EV16" t="n">
-        <v>2.018336272158194e-05</v>
+        <v>3.50957839145849e-06</v>
       </c>
       <c r="EW16" t="n">
-        <v>2.958558070531581e-05</v>
+        <v>1.947214877873193e-05</v>
       </c>
       <c r="EX16" t="n">
-        <v>6.549867521243868e-06</v>
+        <v>1.531505859020399e-06</v>
       </c>
       <c r="EY16" t="n">
-        <v>1.344643624179298e-05</v>
+        <v>2.60089054791024e-05</v>
       </c>
       <c r="EZ16" t="n">
-        <v>4.667273969971575e-06</v>
+        <v>2.287033794345916e-06</v>
       </c>
       <c r="FA16" t="n">
-        <v>1.370563677483005e-05</v>
+        <v>9.878386663331185e-06</v>
       </c>
       <c r="FB16" t="n">
-        <v>1.957395625140634e-06</v>
+        <v>8.755610906518996e-06</v>
       </c>
       <c r="FC16" t="n">
-        <v>7.409650606859941e-06</v>
+        <v>9.768864401848987e-06</v>
       </c>
       <c r="FD16" t="n">
-        <v>8.633493052911945e-06</v>
+        <v>6.430385838029906e-06</v>
       </c>
       <c r="FE16" t="n">
-        <v>4.249952326063067e-06</v>
+        <v>1.112476184061961e-06</v>
       </c>
       <c r="FF16" t="n">
-        <v>6.541444008689723e-07</v>
+        <v>6.807197678426746e-06</v>
       </c>
       <c r="FG16" t="n">
-        <v>1.908342528622597e-05</v>
+        <v>2.948200972241466e-06</v>
       </c>
       <c r="FH16" t="n">
-        <v>1.640394657442812e-05</v>
+        <v>1.459391023672651e-05</v>
       </c>
       <c r="FI16" t="n">
-        <v>7.865729457989801e-06</v>
+        <v>1.150639150182542e-06</v>
       </c>
       <c r="FJ16" t="n">
-        <v>3.382412614882924e-06</v>
+        <v>2.141433105862234e-05</v>
       </c>
       <c r="FK16" t="n">
-        <v>1.847177009040024e-05</v>
+        <v>6.626473805226851e-06</v>
       </c>
       <c r="FL16" t="n">
-        <v>7.282735623448389e-07</v>
+        <v>1.591429099789821e-05</v>
       </c>
       <c r="FM16" t="n">
-        <v>5.012732799514197e-06</v>
+        <v>1.005792637442937e-05</v>
       </c>
       <c r="FN16" t="n">
-        <v>7.824158274161164e-06</v>
+        <v>8.238501322921365e-06</v>
       </c>
       <c r="FO16" t="n">
-        <v>1.71109422808513e-05</v>
+        <v>1.087856071535498e-05</v>
       </c>
       <c r="FP16" t="n">
-        <v>6.59998750052182e-06</v>
+        <v>1.836687988543417e-05</v>
       </c>
       <c r="FQ16" t="n">
-        <v>1.23727577374666e-05</v>
+        <v>7.980818918440491e-05</v>
       </c>
       <c r="FR16" t="n">
-        <v>1.607737976883072e-05</v>
+        <v>1.849375985329971e-05</v>
       </c>
       <c r="FS16" t="n">
-        <v>1.653865547268651e-05</v>
+        <v>4.767370046465658e-05</v>
       </c>
       <c r="FT16" t="n">
-        <v>3.764195753319655e-06</v>
+        <v>0.0001145937421824783</v>
       </c>
       <c r="FU16" t="n">
-        <v>2.112010224664118e-05</v>
+        <v>1.185090513899922e-05</v>
       </c>
       <c r="FV16" t="n">
-        <v>1.142515611718409e-05</v>
+        <v>7.020205885055475e-06</v>
       </c>
       <c r="FW16" t="n">
-        <v>1.185492692457046e-06</v>
+        <v>3.043640936084557e-05</v>
       </c>
       <c r="FX16" t="n">
-        <v>9.243560270988382e-06</v>
+        <v>9.30363512452459e-06</v>
       </c>
       <c r="FY16" t="n">
-        <v>1.432770386600168e-05</v>
+        <v>9.399808732268866e-06</v>
       </c>
       <c r="FZ16" t="n">
-        <v>1.412886103935307e-05</v>
+        <v>1.844691723817959e-05</v>
       </c>
       <c r="GA16" t="n">
-        <v>5.436692390503595e-06</v>
+        <v>1.363007049803855e-05</v>
       </c>
       <c r="GB16" t="n">
-        <v>4.803519914275967e-06</v>
+        <v>1.946634074556641e-05</v>
       </c>
       <c r="GC16" t="n">
-        <v>1.199330745293992e-05</v>
+        <v>1.732876989990473e-05</v>
       </c>
       <c r="GD16" t="n">
-        <v>2.131497967639007e-05</v>
+        <v>1.442532266082708e-05</v>
       </c>
       <c r="GE16" t="n">
-        <v>2.415161179669667e-05</v>
+        <v>1.956660889845807e-05</v>
       </c>
       <c r="GF16" t="n">
-        <v>9.529736416880041e-06</v>
+        <v>3.053110776818357e-05</v>
       </c>
       <c r="GG16" t="n">
-        <v>6.810800186940469e-06</v>
+        <v>1.47095306601841e-06</v>
       </c>
     </row>
   </sheetData>
